--- a/Input/search_query.xlsx
+++ b/Input/search_query.xlsx
@@ -5,23 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D3E366-1909-46CE-83F3-F872A168DBAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3C42D6-F4A1-454D-98F0-78AFAAF51BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Devendra Fadnavis" sheetId="1" r:id="rId1"/>
-    <sheet name="Eknath Shinde" sheetId="7" r:id="rId2"/>
-    <sheet name="Prakash Abitkar" sheetId="6" r:id="rId3"/>
-    <sheet name="Ravindra Chavan" sheetId="3" r:id="rId4"/>
-    <sheet name="Ashish Shelar" sheetId="4" r:id="rId5"/>
-    <sheet name="Chandrakant Patil" sheetId="8" r:id="rId6"/>
-    <sheet name="Chandrashekhar Bawankule" sheetId="9" r:id="rId7"/>
-    <sheet name="Siddharth Shirole" sheetId="5" r:id="rId8"/>
+    <sheet name="DF Birthday" sheetId="10" r:id="rId1"/>
+    <sheet name="Dhankar Resignation" sheetId="11" r:id="rId2"/>
+    <sheet name="Devendra Fadnavis" sheetId="1" r:id="rId3"/>
+    <sheet name="Eknath Shinde" sheetId="7" r:id="rId4"/>
+    <sheet name="Prakash Abitkar" sheetId="6" r:id="rId5"/>
+    <sheet name="Ravindra Chavan" sheetId="3" r:id="rId6"/>
+    <sheet name="Ashish Shelar" sheetId="4" r:id="rId7"/>
+    <sheet name="Chandrakant Patil" sheetId="8" r:id="rId8"/>
+    <sheet name="Chandrashekhar Bawankule" sheetId="9" r:id="rId9"/>
+    <sheet name="Siddharth Shirole" sheetId="5" r:id="rId10"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DF Birthday'!$A$1:$A$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dhankar Resignation'!$A$1:$A$76</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="566">
   <si>
     <t>devendra fadnavis</t>
   </si>
@@ -1291,13 +1297,463 @@
   </si>
   <si>
     <t>ravindra chavan latest news</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस साजरा  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस सेवादिवस  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस पुणे उपक्रम  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस मुख्यमंत्री सहाय्यता निधी  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस शुभेच्छा  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस बातम्या महाराष्ट्र  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस दान कार्यक्रम  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस गडचिरोली  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस सामाजिक कार्य  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस फोटो व्हिडिओ  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस भाजप कार्यकर्ते  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस नागपूर  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस अमृता फडणवीस  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस रक्तदान शिबिर  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस समाजसेवा  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस पायाभूत सुविधा उपक्रम  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस पर्यावरण संरक्षण  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस हरित महाराष्ट्र  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस जलयुक्त शिवार  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस गडचिरोली वृक्षारोपण  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस स्मार्ट सिटी प्रकल्प  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस महामार्ग विकास  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस शाश्वत विकास  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस सौर ऊर्जा योजना  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाढदिवस समृद्धी महामार्ग  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन उत्सव  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन सेवा दिवस  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन पुणे कार्यक्रम  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन मुख्यमंत्री राहत कोष  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन शुभकामनाएं  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन समाचार महाराष्ट्र  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन चैरिटी इवेंट  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन गडचिरोली  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन सामाजिक कार्य  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन फोटो वीडियो  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन भाजपा कार्यकर्ता  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन नागपुर  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन अमृता फडणवीस  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन रक्तदान शिविर  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन नरेंद्र मोदी शुभकामनाएं  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन बुनियादी ढांचा पहल  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन पर्यावरण संरक्षण  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन हरित महाराष्ट्र  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन जलयुक्त शिविर  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन गडचिरोली वृक्षारोपण  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन स्मार्ट सिटी परियोजना  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन महामार्ग विकास  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन सतत विकास  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन सौर ऊर्जा योजना  </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जन्मदिन समृद्धि महामार्ग  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday celebration  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday Seva Diwas  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday Pune events  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday Chief Minister Relief Fund  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday wishes site:x.com  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday Maharashtra news  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday charity programs  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday Gadchiroli  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday social initiatives  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday photos videos  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday BJP workers  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday Nagpur events  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday Amruta Fadnavis  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday blood donation camp  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday Narendra Modi wishes  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday infrastructure initiatives  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday environmental efforts  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday Green Maharashtra  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday Jalyukt Shivar  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday Gadchiroli tree plantation  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday Smart City projects  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday highway development  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday sustainable development  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday solar energy initiatives  </t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis birthday Samruddhi Expressway</t>
+  </si>
+  <si>
+    <t>जगदीप धनखर उपराष्ट्रपती राजीनामा  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा आरोग्य कारण  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा राज्यसभा सभापती  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा बातम्या site:x.com  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा 2025 महाराष्ट्र  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा नरेंद्र मोदी प्रतिक्रिया  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा काँग्रेस टीका  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा पश्चिम बंगाल  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा राजकीय अटकळ  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा राष्ट्रपती द्रौपदी मुर्मू  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा निवडणूक आयोग  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा जयराम रमेश  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा न्यायपालिका वाद  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा नितीश कुमार अटकळ  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा संसद मॉन्सून सत्र  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा बिजेपी रणनीती  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा विरोधी पक्ष प्रतिक्रिया  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा राजस्थान कनेक्शन  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा किसान पुत्र  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा हरिवंश अटकळ  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा संसद व्यवसाय सल्लागार समिती  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा यशवंत वर्मा प्रकरण  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा दिल्ली अँगियोप्लास्टी  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा राजकीय षडयंत्र  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर राजीनामा उपसभापती जबाबदारी  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर उपराष्ट्रपति इस्तीफा  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा स्वास्थ्य कारण  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा राज्यसभा अध्यक्ष  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा समाचार site:x.com  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा 2025 महाराष्ट्र  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा नरेंद्र मोदी प्रतिक्रिया  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा कांग्रेस आलोचना  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा पश्चिम बंगाल  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा राजनीतिक अटकलें  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा राष्ट्रपति द्रौपदी मुर्मू  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा चुनाव आयोग  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा जयराम रमेश  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा न्यायपालिका विवाद  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा नीतीश कुमार अटकलें  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा संसद मॉनसून सत्र  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा बीजेपी रणनीति  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा विपक्षी प्रतिक्रिया  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा राजस्थान कनेक्शन  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा किसान पुत्र  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा हरिवंश अटकलें  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा संसद व्यवसाय सलाहकार समिति  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा यशवंत वर्मा मामला  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा दिल्ली एंजियोप्लास्टी  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा राजनीतिक साजिश  </t>
+  </si>
+  <si>
+    <t>जगदीप धनखर इस्तीफा उपाध्यक्ष जिम्मेदारी  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar Vice President resignation  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation health reasons  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Rajya Sabha Chairman  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation news site:x.com  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation 2025 Maharashtra  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Narendra Modi reaction  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Congress criticism  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation West Bengal  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation political speculation  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation President Droupadi Murmu  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Election Commission  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Jairam Ramesh  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation judiciary controversy  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Nitish Kumar speculation  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Parliament Monsoon Session  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation BJP strategy  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation opposition reaction  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Rajasthan connection  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Kisan Putra  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Harivansh speculation  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Business Advisory Committee  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Yashwant Varma case  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Delhi angioplasty  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation political conspiracy  </t>
+  </si>
+  <si>
+    <t>Jagdeep Dhankhar resignation Deputy Chairman duties</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1309,6 +1765,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1331,14 +1801,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1616,6 +2090,1200 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBAA2A48-F74A-428E-A474-E7E2B0224AE2}">
+  <dimension ref="A1:A76"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A56" r:id="rId1" display="http://x.com/" xr:uid="{D7EEFFD4-6C2C-47EF-BE34-7E2CA27797F0}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D4577D-FE10-42FD-B10A-D28414797A5F}">
+  <dimension ref="A1:A79"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>243</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB4A1374-30FD-4B53-B704-0480A0FBF33D}">
+  <dimension ref="A1:A76"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" r:id="rId1" display="http://x.com/" xr:uid="{E8684EE2-6127-4F55-B488-0B95874D9B35}"/>
+    <hyperlink ref="A30" r:id="rId2" display="http://x.com/" xr:uid="{6638835F-4F41-4FA3-AEEA-1357500FCB21}"/>
+    <hyperlink ref="A55" r:id="rId3" display="http://x.com/" xr:uid="{BC0BA897-4E54-4D91-8260-6ED872577DBA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2153,7 +3821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F7DD1D-0DFC-440F-988C-050CA65FFA2F}">
   <dimension ref="A1:A185"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3088,7 +4756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C494B66-AEA5-4CCE-888E-96E7151CA2B5}">
   <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3338,7 +5006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13BB4D98-1E3A-4E3C-ACBA-9B32A23C1612}">
   <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3421,7 +5089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20836306-9997-450D-A55C-BA5D93912EB9}">
   <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3504,7 +5172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3999BA3D-14F7-4974-A4C1-C319E42C52A3}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3519,7 +5187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C323B3F7-4FF2-40F4-B949-CB50AFBFD4BF}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3532,409 +5200,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D4577D-FE10-42FD-B10A-D28414797A5F}">
-  <dimension ref="A1:A79"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>243</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Input/search_query.xlsx
+++ b/Input/search_query.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3C42D6-F4A1-454D-98F0-78AFAAF51BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98C0C43-F52F-4A28-90C3-696364CE4F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DF Birthday" sheetId="10" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Chandrakant Patil" sheetId="8" r:id="rId8"/>
     <sheet name="Chandrashekhar Bawankule" sheetId="9" r:id="rId9"/>
     <sheet name="Siddharth Shirole" sheetId="5" r:id="rId10"/>
+    <sheet name="Shinraj Singh Chauhan" sheetId="12" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DF Birthday'!$A$1:$A$76</definedName>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="566">
   <si>
     <t>devendra fadnavis</t>
   </si>
@@ -2888,6 +2889,21 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71AA6F2-96E2-41C0-846E-4C4726501A64}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB4A1374-30FD-4B53-B704-0480A0FBF33D}">
   <dimension ref="A1:A76"/>

--- a/Input/search_query.xlsx
+++ b/Input/search_query.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98C0C43-F52F-4A28-90C3-696364CE4F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179A30CC-BCBD-48BE-89B7-0C4EC904B39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DF Birthday" sheetId="10" r:id="rId1"/>
@@ -50,10 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="566">
-  <si>
-    <t>devendra fadnavis</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="660">
   <si>
     <t>Keyword</t>
   </si>
@@ -517,18 +514,6 @@
     <t>देवेंद्र फडणवीस वाद</t>
   </si>
   <si>
-    <t>Devendra Fadnavis MahaStride launch 2025</t>
-  </si>
-  <si>
-    <t>Devendra Fadnavis Uddhav Thackeray remarks</t>
-  </si>
-  <si>
-    <t>देवेंद्र फडणवीस उद्धव ठाकरे बयान</t>
-  </si>
-  <si>
-    <t>देवेंद्र फडणवीस उद्धव ठाकरे टीका</t>
-  </si>
-  <si>
     <t>Devendra Fadnavis BJP Maharashtra leadership</t>
   </si>
   <si>
@@ -1748,13 +1733,310 @@
   </si>
   <si>
     <t>Jagdeep Dhankhar resignation Deputy Chairman duties</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस विधानपरिषद</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis new project</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नया प्रकल्प</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नवा प्रकल्प</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis public rally</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सार्वजनिक सभा</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जाहीर सभा</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis on Rahul Gandhi</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राहुल गांधी पर</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राहुल गांधींवर</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Nagpur Pune Vande Bharat 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नागपुर पुणे वंदे भारत 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नागपूर पुणे वंदे भारत 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Dharavi redevelopment 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस धारावी पुनर्विकास 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis solar power push 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सोलर पावर प्रोत्साहन 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सौर ऊर्जा प्रोत्साहन 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Garud Drishti project 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस गरुड दृष्टी प्रकल्प 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Raksha Bandhan Ladki Bahin 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस रक्षाबंधन लाडकी बहिण 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस रक्षाबंधन लाडकी बहीण 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis vote rigging controversy 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मतदान खरेदी विवाद 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मतदान खरेदी वाद 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Sharad Pawar remarks</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस शरद पवार टिप्पणी</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस शरद पवार टीका</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis OBC speech 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस ओबीसी भाषण 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis cyber security initiative</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सायबर सुरक्षा पहल</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सायबर सुरक्षा उपक्रम</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Nitin Gadkari meeting</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नितिन गडकरी मुलाकात</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नितिन गडकरी भेट</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Chief Minister tenure 2022-present</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मुख्यमंत्री कार्यकाल 2022-वर्तमान</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मुख्यमंत्री कार्यकाळ 2022-वर्तमान</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis role in Mahayuti alliance</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महायुति गठबंधन भूमिका</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महायुति आघाडी भूमिका</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Nagpur South West constituency</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नागपुर साउथ वेस्ट निर्वाचन क्षेत्र</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नागपूर साउथ वेस्ट मतदारसंघ</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis infrastructure policies Maharashtra</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र बुनियादी ढांचा नीतियां</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र पायाभूत सुविधा धोरणे</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis vote rigging allegations 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मतदान खरेदी आरोप 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Mahayuti alliance strategy</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महायुति गठबंधन रणनीति</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महायुति आघाडी रणनीती</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis drought management Maharashtra</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र सूखा प्रबंधन</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र दुष्काळ व्यवस्थापन</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis RSS and ABVP background</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस आरएसएस और एबीवीपी पृष्ठभूमि</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस आरएसएस आणि एबीव्हीपी पार्श्वभूमी</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Home Ministry portfolio 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस गृह मंत्रालय पोर्टफोलियो 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस गृह खाते पोर्टफोलियो 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Mumbai</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मुंबई</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis this week events 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस इस सप्ताह की घटनाएं 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस या आठवड्याचे कार्यक्रम 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Latur visit 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस लातूर दौरा 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस लातूर भेट 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis environmental initiative 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस पर्यावरण पहल 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस पर्यावरण उपक्रम 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Ladki Bahin scheme 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस लाडकी बहिण योजना 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस लाडकी बहीण योजना 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Sharad Pawar controversy 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस शरद पवार विवाद 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस शरद पवार वाद 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis political activities August 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस अगस्त 2025 राजनीतिक गतिविधियां</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस ऑगस्ट 2025 राजकीय हालचाली</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis public engagements 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सार्वजनिक सहभाग 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जनसंपर्क 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis policy decisions 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नीति निर्णय 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस धोरण निर्णय 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis urban infrastructure projects</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस शहरी बुनियादी ढांचा परियोजनाएं</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस शहरी पायाभूत प्रकल्प</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis economic policies Maharashtra</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र आर्थिक नीतियां</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र आर्थिक धोरणे</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis social welfare schemes 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सामाजिक कल्याण योजनाएं 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सामाजिक कल्याण योजना 2025":30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1784,6 +2066,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1806,11 +2094,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2097,382 +2388,382 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -2491,397 +2782,397 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -2896,7 +3187,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2911,382 +3202,382 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -3301,7 +3592,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A105"/>
+  <dimension ref="A1:A217"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -3309,527 +3600,1087 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" s="4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" s="4" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" s="4" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" s="4" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" s="4" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" s="4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" s="4" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" s="4" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" s="4" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" s="4" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" s="4" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" s="4" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" s="4" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" s="4" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" s="4" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" s="4" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" s="4" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" s="4" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" s="4" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" s="4" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" s="4" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" s="4" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" s="4" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" s="4" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" s="4" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" s="4" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" s="4" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" s="4" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" s="4" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" s="4" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" s="4" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" s="4" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" s="4" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" s="4" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" s="4" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" s="4" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" s="4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" s="4" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" s="4" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" s="4" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162" s="4" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163" s="4" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164" s="4" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165" s="4" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" s="4" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" s="4" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" s="4" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" s="4" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" s="4" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172" s="4" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173" s="4" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174" s="4" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175" s="4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176" s="4" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177" s="4" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178" s="4" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" s="4" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" s="4" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" s="4" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183" s="4" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185" s="4" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187" s="4" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188" s="4" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189" s="4" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190" s="4" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191" s="4" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192" s="4" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" s="4" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195" s="4" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196" s="4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A197" s="4" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A198" s="4" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199" s="4" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A200" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A201" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A202" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A203" s="4" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A204" s="4" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A205" s="4" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A206" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A207" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A208" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>167</v>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A209" s="4" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A210" s="4" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A211" s="4" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A212" s="4" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A213" s="4" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A214" s="4" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A215" s="4" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A216" s="4" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A217" s="4" t="s">
+        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -3844,927 +4695,927 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -4779,242 +5630,242 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -5032,72 +5883,72 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -5115,72 +5966,72 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6046,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5210,7 +6061,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Input/search_query.xlsx
+++ b/Input/search_query.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966F8368-4815-4E8A-8F39-726F274B9CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E09480-52E1-49E9-92FC-95CFDC0EE4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OBC Andolan" sheetId="13" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="1176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="1405">
   <si>
     <t>Keyword</t>
   </si>
@@ -3476,96 +3476,6 @@
     <t>मुख्यमंत्री एकनाथ शिंदे महाराष्ट्र विकास</t>
   </si>
   <si>
-    <t>Deputy Chief Minister Devendra Fadnavis latest news</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस ताज्या बातम्या</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis Maharashtra government 2025</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस महाराष्ट्र सरकार 2025</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis new announcements 2025</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस नवीन घोषणा 2025</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis public interaction</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस जनतेशी संवाद</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis Maharashtra assembly 2025</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस विधानसभा 2025</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis press conference</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस पत्रकार परिषद</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis Mahayuti alliance</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस महायुती</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis infrastructure projects</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस पायाभूत सुविधा प्रकल्प</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis public welfare schemes</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस जनकल्याण योजना</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis urban development</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस शहरी विकास</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis rural development</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस ग्रामीण विकास</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis election strategy 2025</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस निवडणूक रणनीती 2025</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis BJP Maharashtra</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस भाजप महाराष्ट्र</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis policy decisions</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस धोरणात्मक निर्णय</t>
-  </si>
-  <si>
-    <t>Deputy Chief Minister Devendra Fadnavis Maharashtra development</t>
-  </si>
-  <si>
-    <t>उपमुख्यमंत्री देवेंद्र फडणवीस महाराष्ट्र विकास</t>
-  </si>
-  <si>
     <t>Chhagan Bhujbal against Maratha inclusion</t>
   </si>
   <si>
@@ -3573,6 +3483,783 @@
   </si>
   <si>
     <t>OBC reservation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devendra Fadnavis Yavatmal visit September 2025  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस यवतमाळ भेट सप्टेंबर २०२५  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devendra Fadnavis Aadi Karmayogi Abhiyan news  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस आदि कर्मयोगी अभियान समाचार  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस आदि कर्मयोगी अभियान बातम्या  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devendra Fadnavis Iowa MoU latest  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस आयोवा एमओयू ताजा समाचार  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस आयोवा एमओयू नवीन बातम्या  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devendra Fadnavis Tata Technologies agreement  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस टाटा टेक्नॉलॉजीज करार  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस टाटा टेक्नॉलॉजीज करार बातम्या  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devendra Fadnavis tribal welfare schemes September 2025  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस आदिवासी कल्याण योजना सप्टेंबर २०२५  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस आदिवासी कल्याण योजना बातम्या  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devendra Fadnavis solar projects Vidarbha  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस सौर प्रकल्प विदर्भ  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस सौर प्रकल्प विदर्भ बातम्या  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devendra Fadnavis farmer relief heavy rainfall  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस शेतकरी मदत अतिवृष्टी  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस शेतकरी मदत अतिवृष्टी बातम्या  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devendra Fadnavis STRIDE 2025 speech  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस स्ट्राईड २०२५ भाषण  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस स्ट्राईड २०२५ भाषण बातम्या  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devendra Fadnavis Sanjay Raut comments September 2025  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस संजय राऊत टिप्पण्या सप्टेंबर २०२५  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस संजय राऊत टिप्पण्या बातम्या  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devendra Fadnavis book release Jawaharlal Darda  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस पुस्तक प्रकाशन जवाहरलाल दर्डा  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस पुस्तक प्रकाशन जवाहरलाल दर्डा बातम्या  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devendra Fadnavis development works inauguration Yavatmal  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस विकास कामे उद्घाटन यवतमाळ  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस विकास कामे उद्घाटन यवतमाळ बातम्या  </t>
+  </si>
+  <si>
+    <t>Eknath Shinde Idea Exchange Conclave September 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे आयडिया एक्सचेंज कॉन्क्लेव्ह सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे आयडिया एक्सचेंज कॉन्क्लेव्ह बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde racecourse Central Park development Mumbai September 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे रेसकोर्स सेंट्रल पार्क विकास मुंबई सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे रेसकोर्स सेंट्रल पार्क विकास मुंबई बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde rivalry Fadnavis denial September 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे फडणवीस वैर नाकारणे सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे फडणवीस वैर नाकारणे बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Elphinstone bridge demolition rehab September 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे एल्फिन्स्टन ब्रिज तोडफोड पुनर्वसन सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे एल्फिन्स्टन ब्रिज तोडफोड पुनर्वसन बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Jarange Patil Maratha agitation September 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे जरंगे पाटील मराठा आंदोलन सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे जरंगे पाटील मराठा आंदोलन बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Shiv Sena cadre BMC elections September 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे शिवसेना कार्यकर्ते बीएमसी निवडणुका सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे शिवसेना कार्यकर्ते बीएमसी निवडणुका बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Lalbaugcha Raja Ganeshotsav 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे लालबaugचा राजा गणेशोत्सव २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे लालबaugचा राजा गणेशोत्सव बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Vice President meeting September 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे उपराष्ट्रपती भेट सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे उपराष्ट्रपती भेट बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Mumbai infrastructure projects September 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे मुंबई पायाभूत सुविधा प्रकल्प सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे मुंबई पायाभूत सुविधा प्रकल्प बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Maratha reservation comments September 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे मराठा आरक्षण टिप्पणी सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे मराठा आरक्षण टिप्पणी बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Shiv Sena foundation day September 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे शिवसेना वर्धापन दिन सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे शिवसेना वर्धापन दिन बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde grandson interview viral September 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे नातू मुलाखत व्हायरल सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे नातू मुलाखत व्हायरल बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Dahisar toll naka relocation September 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे दहाणू टोल नाका स्थलांतर सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे दहाणू टोल नाका स्थलांतर बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Nepal tourists stranded assistance September 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे नेपाळ पर्यटक अडकले मदत सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे नेपाळ पर्यटक अडकले मदत बातम्या</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar health policy reforms September 2025</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर आरोग्य धोरण सुधारणा सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर आरोग्य धोरण सुधारणा बातम्या</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar medical officer recruitment September 2025</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर वैद्यकीय अधिकारी भरती सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर वैद्यकीय अधिकारी भरती बातम्या</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar Cancer Day Care Centres launch</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर कर्करोग डे केअर सेंटर्स सुरू</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर कर्करोग डे केअर सेंटर्स बातम्या</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar GBS outbreak response September 2025</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर जीबीएस उद्रेक प्रतिसाद सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर जीबीएस उद्रेक प्रतिसाद बातम्या</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar health tourism policy accreditation</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर आरोग्य पर्यटन धोरण मान्यता</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर आरोग्य पर्यटन धोरण मान्यता बातम्या</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar leprosy eradication committee September 2025</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर कुष्ठरोग निर्मूलन समिती सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर कुष्ठरोग निर्मूलन समिती बातम्या</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर अवयव दान मोहीम ऑगस्ट २०२५</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर अवयव दान मोहीम बातम्या</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar clean water law proposal September 2025</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर स्वच्छ पाणी कायदा प्रस्ताव सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर स्वच्छ पाणी कायदा प्रस्ताव बातम्या</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar Arogya Sanman 2025 speech</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर आरोग्य सन्मान २०२५ भाषण</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर आरोग्य सन्मान २०२५ भाषण बातम्या</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar TB-Free Panchayats campaign</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर क्षयरोगमुक्त पंचायत मोहीम</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर क्षयरोगमुक्त पंचायत मोहीम बातम्या</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar nursing staff service rules September 2025</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर नर्सिंग कर्मचारी सेवा नियम सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर नर्सिंग कर्मचारी सेवा नियम बातम्या</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar Kolhapur cooperative sector September 2025</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर कोल्हापूर सहकारी क्षेत्र सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>प्रकाश अबितकर कोल्हापूर सहकारी क्षेत्र बातम्या</t>
+  </si>
+  <si>
+    <t>Ravindra Chavan Dombivli Janmashtami celebrations September 2025</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण डोंबिवली जन्माष्टमी उत्सव सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण डोंबिवली जन्माष्टमी उत्सव बातम्या</t>
+  </si>
+  <si>
+    <t>Ravindra Chavan BJP membership drive September 2025</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण भाजप सदस्यता अभियान सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण भाजप सदस्यता अभियान बातम्या</t>
+  </si>
+  <si>
+    <t>Ravindra Chavan local body election strategy 2025</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण स्थानिक स्वराज्य संस्था निवडणूक रणनीती २०२५</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण स्थानिक स्वराज्य संस्था निवडणूक रणनीती बातम्या</t>
+  </si>
+  <si>
+    <t>Ravindra Chavan Yuva Morcha training programs September 2025</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण युवा मोर्चा प्रशिक्षण कार्यक्रम सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण युवा मोर्चा प्रशिक्षण कार्यक्रम बातम्या</t>
+  </si>
+  <si>
+    <t>Ravindra Chavan Mahila Morcha outreach September 2025</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण महिला मोर्चा संपर्क अभियान सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण महिला मोर्चा संपर्क अभियान बातम्या</t>
+  </si>
+  <si>
+    <t>Ravindra Chavan Karya Vistar Abhiyan progress</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण कार्य विस्तार अभियान प्रगती</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण कार्य विस्तार अभियान प्रगती बातम्या</t>
+  </si>
+  <si>
+    <t>Ravindra Chavan booth-level campaign September 2025</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण बूथ-स्तरीय मोहीम सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण बूथ-स्तरीय मोहीम बातम्या</t>
+  </si>
+  <si>
+    <t>Ravindra Chavan Fadnavis coordination BMC polls</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण फडणवीस समन्वय बीएमसी निवडणुका</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण फडणवीस समन्वय बीएमसी निवडणुका बातम्या</t>
+  </si>
+  <si>
+    <t>Ravindra Chavan RSS coordination Maharashtra September 2025</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण आरएसएस समन्वय महाराष्ट्र सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण आरएसएस समन्वय महाराष्ट्र बातम्या</t>
+  </si>
+  <si>
+    <t>Ravindra Chavan Sangathan Parv review September 2025</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण संघटन पर्व पुनरावलोकन सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण संघटन पर्व पुनरावलोकन बातम्या</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Mumbai building OC policy September 2025</t>
+  </si>
+  <si>
+    <t>आशिष शेलार मुंबई इमारत ओसी धोरण सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>आशिष शेलार मुंबई इमारत ओसी धोरण बातम्या</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Koliwada development plan September 2025</t>
+  </si>
+  <si>
+    <t>आशिष शेलार कोळीवाडा विकास योजना सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>आशिष शेलार कोळीवाडा विकास योजना बातम्या</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Sanjay Raut Asia Cup comments September 2025</t>
+  </si>
+  <si>
+    <t>आशिष शेलार संजय राऊत आशिया कप टिप्पण्या सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>आशिष शेलार संजय राऊत आशिया कप टिप्पण्या बातम्या</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Lalbaugcha Raja auction 2025</t>
+  </si>
+  <si>
+    <t>आशिष शेलार लालबागचा राजा लिलाव २०२५</t>
+  </si>
+  <si>
+    <t>आशिष शेलार लालबागचा राजा लिलाव बातम्या</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Maratha quota clarification September 2025</t>
+  </si>
+  <si>
+    <t>आशिष शेलार मराठा आरक्षण स्पष्टीकरण सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>आशिष शेलार मराठा आरक्षण स्पष्टीकरण बातम्या</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Mumbai pothole repairs Ganeshotsav 2025</t>
+  </si>
+  <si>
+    <t>आशिष शेलार मुंबई खड्डे दुरुस्ती गणेशोत्सव २०२५</t>
+  </si>
+  <si>
+    <t>आशिष शेलार मुंबई खड्डे दुरुस्ती गणेशोत्सव बातम्या</t>
+  </si>
+  <si>
+    <t>Ashish Shelar BMC election strategy September 2025</t>
+  </si>
+  <si>
+    <t>आशिष शेलार बीएमसी निवडणूक रणनीती सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>आशिष शेलार बीएमसी निवडणूक रणनीती बातम्या</t>
+  </si>
+  <si>
+    <t>Ashish Shelar cultural events Mumbai September 2025</t>
+  </si>
+  <si>
+    <t>आशिष शेलार सांस्कृतिक कार्यक्रम मुंबई सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>आशिष शेलार सांस्कृतिक कार्यक्रम मुंबई बातम्या</t>
+  </si>
+  <si>
+    <t>Ashish Shelar IT startup initiatives September 2025</t>
+  </si>
+  <si>
+    <t>आशिष शेलार आयटी स्टार्टअप उपक्रम सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>आशिष शेलार आयटी स्टार्टअप उपक्रम बातम्या</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Ganesh Chaturthi celebrations 2025</t>
+  </si>
+  <si>
+    <t>आशिष शेलार गणेश चतुर्थी उत्सव २०२५</t>
+  </si>
+  <si>
+    <t>आशिष शेलार गणेश चतुर्थी उत्सव बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrakant Patil Global Ganesh Festival 2025</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील जागतिक गणेश उत्सव २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील जागतिक गणेश उत्सव बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrakant Patil Maratha reservation comments September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील मराठा आरक्षण टिप्पणी सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील मराठा आरक्षण टिप्पणी बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrakant Patil IIT-COEP collaboration September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील आयआयटी-सीओईपी सहकार्य सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील आयआयटी-सीओईपी सहकार्य बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrakant Patil Adarsh State Teacher Award 2025</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील आदर्श राज्य शिक्षक पुरस्कार २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील आदर्श राज्य शिक्षक पुरस्कार बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrakant Patil Pune Metro progress review September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील पुणे मेट्रो प्रगती पुनरावलोकन सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील पुणे मेट्रो प्रगती पुनरावलोकन बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrakant Patil Ganeshotsav participation Pune 2025</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील गणेशोत्सव सहभाग पुणे २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील गणेशोत्सव सहभाग पुणे बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrakant Patil women empowerment Mulshi September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील महिला सशक्तीकरण मुळशी सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील महिला सशक्तीकरण मुळशी बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrakant Patil Chhagan Bhujbal ordinance clarification September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील छगन भुजबळ अध्यादेश स्पष्टीकरण सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील छगन भुजबळ अध्यादेश स्पष्टीकरण बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrakant Patil work modules for women September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील महिला काम मॉड्यूल्स सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील महिला काम मॉड्यूल्स बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrakant Patil Kothrud road development funds September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील कोथरूड रस्ते विकास निधी सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील कोथरूड रस्ते विकास निधी बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule health proposals Nagpur September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे नागपूर आरोग्य प्रस्ताव सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे नागपूर आरोग्य प्रस्ताव बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule New Nagpur development project September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे नवीन नागपूर विकास प्रकल्प सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे नवीन नागपूर विकास प्रकल्प बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Rashtraneta to Rashtrapita campaign September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे राष्ट्रनेता ते राष्ट्रपिता अभियान सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे राष्ट्रनेता ते राष्ट्रपिता अभियान बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Maratha reservation committees September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे मराठा आरक्षण समित्या सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे मराठा आरक्षण समित्या बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Rohit Pawar penalty waiver controversy September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे रोहित पवार दंड माफी वाद सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे रोहित पवार दंड माफी वाद बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Ajit Pawar IPS officer video response September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे अजित पवार आयपीएस अधिकारी व्हिडिओ प्रतिसाद सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे अजित पवार आयपीएस अधिकारी व्हिडिओ प्रतिसाद बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Ganeshotsav Anant Chaturdashi 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे गणेशोत्सव अनंत चतुर्दशी २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे गणेशोत्सव अनंत चतुर्दशी बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Nana Patekar meeting September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे नाना पाटेकर भेट सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे नाना पाटेकर भेट बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Maharashtra security bill protest response September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे महाराष्ट्र सुरक्षा विधेयक विरोध प्रतिसाद सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे महाराष्ट्र सुरक्षा विधेयक विरोध प्रतिसाद बातम्या</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule OBC quota justice assurance September 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे ओबीसी आरक्षण न्याय हमी सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे ओबीसी आरक्षण न्याय हमी बातम्या</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Maihar development initiatives September 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान मैहर विकास उपक्रम सितंबर २०२५</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान मैहर विकास उपक्रम बातम्या</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Viksit Krishi Sankalp Abhiyan October 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान विकसित कृषि संकल्प अभियान अक्टूबर २०२५</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान विकसित कृषि संकल्प अभियान बातम्या</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Satna fertilizer supply assurance September 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान सतना खाद पुरवठा आश्वासन सितंबर २०२५</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान सतना खाद पुरवठा आश्वासन बातम्या</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan GST reduction agriculture equipment September 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान जीएसटी कमी कृषि उपकरण सितंबर २०२५</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान जीएसटी कमी कृषि उपकरण बातम्या</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Sehore MGNREGA projects September 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान सिहोर मनरेगा प्रकल्प सितंबर २०२५</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान सिहोर मनरेगा प्रकल्प बातम्या</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan PMAY-G housing allocation Madhya Pradesh September 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान पीएमएवाय-जी गृहनिर्माण वाटप मध्य प्रदेश सितंबर २०२५</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान पीएमएवाय-जी गृहनिर्माण वाटप बातम्या</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Narmada irrigation projects Sehore September 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान नर्मदा सिंचन प्रकल्प सिहोर सितंबर २०२५</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान नर्मदा सिंचन प्रकल्प सिहोर बातम्या</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Union Budget 2025 agriculture focus</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान केंद्रीय बजट २०२५ कृषि केंद्रित</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान केंद्रीय बजट २०२५ कृषि केंद्रित बातम्या</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Sharda Mata Mandir visit September 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान शारदा माता मंदिर भेट सितंबर २०२५</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान शारदा माता मंदिर भेट बातम्या</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Madhya Pradesh budget praise September 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान मध्य प्रदेश बजट प्रशंसा सितंबर २०२५</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान मध्य प्रदेश बजट प्रशंसा बातम्या</t>
   </si>
 </sst>
 </file>
@@ -3596,7 +4283,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3606,6 +4293,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3622,11 +4333,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3917,17 +4633,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1175</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1173</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1174</v>
+        <v>1144</v>
       </c>
     </row>
   </sheetData>
@@ -4342,7 +5058,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A224"/>
+  <dimension ref="A1:A226"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -5313,159 +6029,169 @@
         <v>488</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
+    <row r="194" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="4" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="195" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="3" t="s">
-        <v>1143</v>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>1146</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1172</v>
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>1177</v>
       </c>
     </row>
   </sheetData>
@@ -5475,897 +6201,1110 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F7DD1D-0DFC-440F-988C-050CA65FFA2F}">
-  <dimension ref="A1:A178"/>
+  <dimension ref="A1:A220"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="8.88671875" style="5"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="5" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="5" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="5" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="5" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="5" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="5" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="5" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="5" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="5" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="5" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="5" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="5" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="5" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="5" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="5" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="5" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="5" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="5" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="5" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="5" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="5" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="5" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="5" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="5" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="5" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="5" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="5" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="5" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="5" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" s="5" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" s="5" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" s="5" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="5" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" s="5" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="5" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" s="5" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" s="5" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" s="5" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" s="5" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="5" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" s="5" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" s="5" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="5" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="5" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" s="5" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" s="5" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="5" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" s="5" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" s="5" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="A53" s="5" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" s="5" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="A55" s="5" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="A56" s="5" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="A57" s="5" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" s="5" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="A59" s="5" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="A60" s="5" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="A61" s="5" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="A62" s="5" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="A63" s="5" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="A64" s="5" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="A65" s="5" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="A66" s="5" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="A67" s="5" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="A68" s="5" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="A69" s="5" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="A70" s="5" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="A71" s="5" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="A72" s="5" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="A73" s="5" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="A74" s="5" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="A75" s="5" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="A76" s="5" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="A77" s="5" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="A78" s="5" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+      <c r="A79" s="5" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="A80" s="5" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+      <c r="A81" s="5" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="A82" s="5" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="A83" s="5" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+      <c r="A84" s="5" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+      <c r="A85" s="5" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+      <c r="A86" s="5" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="A87" s="5" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="A88" s="5" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="A89" s="5" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+      <c r="A90" s="5" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="A91" s="5" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="A92" s="5" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+      <c r="A93" s="5" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+      <c r="A94" s="5" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+      <c r="A95" s="5" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+      <c r="A96" s="5" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+      <c r="A97" s="5" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+      <c r="A98" s="5" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+      <c r="A99" s="5" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="100" spans="1:1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="A100" s="5" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+      <c r="A101" s="5" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="A102" s="5" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="A103" s="5" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+      <c r="A104" s="5" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+      <c r="A105" s="5" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="A106" s="5" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+      <c r="A107" s="5" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+      <c r="A108" s="5" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+      <c r="A109" s="5" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+      <c r="A110" s="5" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+      <c r="A111" s="5" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+      <c r="A112" s="5" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+      <c r="A113" s="5" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+      <c r="A114" s="5" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+      <c r="A115" s="5" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+      <c r="A116" s="5" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+      <c r="A117" s="5" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+      <c r="A118" s="5" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+      <c r="A119" s="5" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+      <c r="A120" s="5" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+      <c r="A121" s="5" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+      <c r="A122" s="5" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+      <c r="A123" s="5" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+      <c r="A124" s="5" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
+      <c r="A125" s="5" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+      <c r="A126" s="5" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+      <c r="A127" s="5" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+      <c r="A128" s="5" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+      <c r="A129" s="5" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
+      <c r="A130" s="5" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
+      <c r="A131" s="5" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+      <c r="A132" s="5" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
+      <c r="A133" s="5" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+      <c r="A134" s="5" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+      <c r="A135" s="5" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+      <c r="A136" s="5" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
+      <c r="A137" s="5" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
+      <c r="A138" s="5" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
+      <c r="A139" s="5" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
+      <c r="A140" s="5" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+      <c r="A141" s="5" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
+      <c r="A142" s="5" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
+      <c r="A143" s="5" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
+      <c r="A144" s="5" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
+      <c r="A145" s="5" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
+      <c r="A146" s="5" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
+      <c r="A147" s="5" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
+      <c r="A148" s="5" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A149" s="3" t="s">
+      <c r="A149" s="5" t="s">
         <v>1113</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
+      <c r="A150" s="5" t="s">
         <v>1114</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
+      <c r="A151" s="5" t="s">
         <v>1115</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
+      <c r="A152" s="5" t="s">
         <v>1116</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
+      <c r="A153" s="5" t="s">
         <v>1117</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
+      <c r="A154" s="5" t="s">
         <v>1118</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
+      <c r="A155" s="5" t="s">
         <v>1119</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
+      <c r="A156" s="5" t="s">
         <v>1120</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
+      <c r="A157" s="5" t="s">
         <v>1121</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
+      <c r="A158" s="5" t="s">
         <v>1122</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
+      <c r="A159" s="5" t="s">
         <v>1123</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
+      <c r="A160" s="5" t="s">
         <v>1124</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
+      <c r="A161" s="5" t="s">
         <v>1125</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
+      <c r="A162" s="5" t="s">
         <v>1126</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
+      <c r="A163" s="5" t="s">
         <v>1127</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
+      <c r="A164" s="5" t="s">
         <v>1128</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
+      <c r="A165" s="5" t="s">
         <v>1129</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
+      <c r="A166" s="5" t="s">
         <v>1130</v>
       </c>
     </row>
-    <row r="167" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" s="5" t="s">
         <v>1131</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
+      <c r="A168" s="5" t="s">
         <v>1132</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
+      <c r="A169" s="5" t="s">
         <v>1133</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
+      <c r="A170" s="5" t="s">
         <v>1134</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
+      <c r="A171" s="5" t="s">
         <v>1135</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
+      <c r="A172" s="5" t="s">
         <v>1136</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
+      <c r="A173" s="5" t="s">
         <v>1137</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
+      <c r="A174" s="5" t="s">
         <v>1138</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
+      <c r="A175" s="5" t="s">
         <v>1139</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
+      <c r="A176" s="5" t="s">
         <v>1140</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
+      <c r="A177" s="5" t="s">
         <v>1141</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
+    <row r="178" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="7" t="s">
         <v>1142</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" s="5" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" s="5" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" s="5" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" s="5" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183" s="5" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184" s="5" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185" s="5" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186" s="5" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187" s="5" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188" s="5" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189" s="5" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190" s="5" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191" s="5" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192" s="5" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" s="5" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194" s="5" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195" s="5" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196" s="5" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A197" s="5" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A198" s="5" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199" s="5" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A200" s="5" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A201" s="5" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A202" s="5" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A203" s="5" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A204" s="5" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A205" s="5" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A206" s="5" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A207" s="5" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A208" s="5" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A209" s="5" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A210" s="5" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A211" s="5" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A212" s="5" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A213" s="5" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A214" s="5" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A215" s="5" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A216" s="5" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A217" s="5" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A218" s="5" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A219" s="5" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A220" s="5" t="s">
+        <v>1219</v>
       </c>
     </row>
   </sheetData>
@@ -6375,1156 +7314,1159 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C494B66-AEA5-4CCE-888E-96E7151CA2B5}">
-  <dimension ref="A1:J198"/>
+  <dimension ref="A1:I233"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="43.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="H2" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G2" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G3" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G4" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="H5" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G5" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="H6" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>33</v>
       </c>
-      <c r="H7" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G7" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="H8" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G8" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="H9" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G9" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>36</v>
       </c>
-      <c r="H10" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G10" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="H11" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G11" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>38</v>
       </c>
-      <c r="H12" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G12" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="H13" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G13" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="H14" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G14" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="H15" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G15" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="H16" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G16" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="H17" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G17" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>44</v>
       </c>
-      <c r="H18" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G18" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
-      <c r="H19" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>46</v>
       </c>
-      <c r="H20" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G20" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>47</v>
       </c>
-      <c r="H21" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G21" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>48</v>
       </c>
-      <c r="H22" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G22" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
-      <c r="H23" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G23" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>50</v>
       </c>
-      <c r="H24" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G24" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>51</v>
       </c>
-      <c r="H25" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G25" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>52</v>
       </c>
-      <c r="H26" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G26" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>53</v>
       </c>
-      <c r="H27" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G27" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>54</v>
       </c>
-      <c r="H28" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G28" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>55</v>
       </c>
-      <c r="H29" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G29" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>56</v>
       </c>
-      <c r="H30" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G30" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>57</v>
       </c>
-      <c r="H31" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G31" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>58</v>
       </c>
-      <c r="H32" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G32" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>59</v>
       </c>
-      <c r="H33" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G33" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>60</v>
       </c>
-      <c r="H34" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G34" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>61</v>
       </c>
-      <c r="H35" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G35" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>62</v>
       </c>
-      <c r="H36" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G36" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>63</v>
       </c>
-      <c r="H37" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G37" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>64</v>
       </c>
-      <c r="H38" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G38" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>65</v>
       </c>
-      <c r="H39" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G39" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>66</v>
       </c>
-      <c r="H40" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G40" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>67</v>
       </c>
-      <c r="H41" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G41" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>68</v>
       </c>
-      <c r="H42" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G42" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>69</v>
       </c>
-      <c r="H43" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G43" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>70</v>
       </c>
-      <c r="H44" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G44" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>71</v>
       </c>
-      <c r="H45" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G45" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>72</v>
       </c>
-      <c r="H46" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G46" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>827</v>
       </c>
-      <c r="H47" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G47" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>828</v>
       </c>
-      <c r="H48" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G48" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>829</v>
       </c>
-      <c r="H49" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G49" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>830</v>
       </c>
-      <c r="H50" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G50" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>831</v>
       </c>
-      <c r="H51" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G51" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>832</v>
       </c>
-      <c r="H52" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G52" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>833</v>
       </c>
-      <c r="H53" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G53" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>834</v>
       </c>
-      <c r="H54" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G54" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>835</v>
       </c>
-      <c r="H55" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G55" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>836</v>
       </c>
-      <c r="H56" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G56" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>837</v>
       </c>
-      <c r="H57" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G57" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>838</v>
       </c>
-      <c r="H58" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G58" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>839</v>
       </c>
-      <c r="H59" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G59" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>840</v>
       </c>
-      <c r="H60" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G60" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>841</v>
       </c>
-      <c r="H61" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G61" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>842</v>
       </c>
-      <c r="H62" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G62" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>843</v>
       </c>
-      <c r="H63" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G63" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>844</v>
       </c>
-      <c r="H64" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G64" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>845</v>
       </c>
-      <c r="H65" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G65" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>846</v>
       </c>
-      <c r="H66" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G66" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>847</v>
       </c>
-      <c r="H67" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G67" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>848</v>
       </c>
-      <c r="H68" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G68" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>849</v>
       </c>
-      <c r="H69" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G69" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>850</v>
       </c>
-      <c r="H70" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G70" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>851</v>
       </c>
-      <c r="H71" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G71" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>852</v>
       </c>
-      <c r="H72" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G72" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>853</v>
       </c>
-      <c r="H73" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G73" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>854</v>
       </c>
-      <c r="H74" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G74" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>855</v>
       </c>
-      <c r="H75" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G75" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>856</v>
       </c>
-      <c r="H76" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G76" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>857</v>
       </c>
-      <c r="H77" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G77" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>858</v>
       </c>
-      <c r="H78" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G78" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>859</v>
       </c>
-      <c r="H79" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G79" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>860</v>
       </c>
-      <c r="H80" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G80" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>861</v>
       </c>
-      <c r="H81" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G81" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>862</v>
       </c>
-      <c r="H82" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G82" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>863</v>
       </c>
-      <c r="H83" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G83" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>864</v>
       </c>
-      <c r="H84" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G84" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>865</v>
       </c>
-      <c r="H85" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G85" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>866</v>
       </c>
-      <c r="H86" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G86" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>867</v>
       </c>
-      <c r="H87" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G87" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>868</v>
       </c>
-      <c r="H88" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G88" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>869</v>
       </c>
-      <c r="H89" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G89" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>870</v>
       </c>
-      <c r="H90" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G90" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>871</v>
       </c>
-      <c r="H91" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G91" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>872</v>
       </c>
-      <c r="H92" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G92" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>873</v>
       </c>
-      <c r="H93" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G93" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>874</v>
       </c>
-      <c r="H94" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G94" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>875</v>
       </c>
-      <c r="H95" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G95" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>876</v>
       </c>
-      <c r="H96" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G96" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>877</v>
       </c>
-      <c r="H97" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G97" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>878</v>
       </c>
-      <c r="H98" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G98" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>879</v>
       </c>
-      <c r="H99" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G99" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>880</v>
       </c>
-      <c r="H100" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G100" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>881</v>
       </c>
-      <c r="H101" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G101" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>882</v>
       </c>
-      <c r="H102" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G102" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>883</v>
       </c>
-      <c r="H103" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G103" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>884</v>
       </c>
-      <c r="H104" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G104" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>885</v>
       </c>
-      <c r="H105" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G105" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>886</v>
       </c>
-      <c r="H106" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G106" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>887</v>
       </c>
-      <c r="H107" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G107" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>888</v>
       </c>
-      <c r="H108" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G108" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>889</v>
       </c>
-      <c r="H109" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G109" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>890</v>
       </c>
-      <c r="H110" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G110" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>891</v>
       </c>
-      <c r="H111" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G111" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>892</v>
       </c>
-      <c r="H112" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G112" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>893</v>
       </c>
-      <c r="H113" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G113" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>894</v>
       </c>
-      <c r="H114" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G114" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>895</v>
       </c>
-      <c r="H115" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G115" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>896</v>
       </c>
-      <c r="H116" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G116" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>897</v>
       </c>
-      <c r="H117" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G117" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>898</v>
       </c>
-      <c r="H118" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G118" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>899</v>
       </c>
-      <c r="H119" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G119" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>900</v>
       </c>
-      <c r="H120" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G120" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>901</v>
       </c>
-      <c r="H121" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G121" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>902</v>
       </c>
-      <c r="H122" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G122" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>903</v>
       </c>
-      <c r="H123" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G123" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>904</v>
       </c>
-      <c r="H124" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G124" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>905</v>
       </c>
-      <c r="H125" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G125" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>906</v>
       </c>
-      <c r="H126" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G126" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>907</v>
       </c>
-      <c r="H127" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G127" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>908</v>
       </c>
-      <c r="H128" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G128" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>909</v>
       </c>
-      <c r="H129" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G129" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>910</v>
       </c>
-      <c r="H130" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G130" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>911</v>
       </c>
-      <c r="H131" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G131" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>912</v>
       </c>
-      <c r="H132" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G132" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>913</v>
       </c>
-      <c r="H133" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G133" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>914</v>
       </c>
-      <c r="H134" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G134" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>915</v>
       </c>
-      <c r="H135" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G135" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>916</v>
       </c>
-      <c r="H136" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G136" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>917</v>
       </c>
-      <c r="H137" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G137" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>918</v>
       </c>
-      <c r="H138" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G138" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>919</v>
       </c>
-      <c r="H139" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G139" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>920</v>
       </c>
-      <c r="H140" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G140" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>921</v>
       </c>
-      <c r="H141" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G141" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>922</v>
       </c>
-      <c r="H142" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G142" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>923</v>
       </c>
-      <c r="H143" t="s">
-        <v>825</v>
-      </c>
-      <c r="J143" s="2"/>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G143" t="s">
+        <v>825</v>
+      </c>
+      <c r="I143" s="2"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>924</v>
       </c>
-      <c r="H144" t="s">
+      <c r="G144" t="s">
         <v>826</v>
       </c>
     </row>
@@ -7663,8 +8605,8 @@
         <v>951</v>
       </c>
     </row>
-    <row r="172" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
+    <row r="172" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="5" t="s">
         <v>1086</v>
       </c>
     </row>
@@ -7796,6 +8738,181 @@
     <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>1112</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>1254</v>
       </c>
     </row>
   </sheetData>
@@ -7805,7 +8922,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13BB4D98-1E3A-4E3C-ACBA-9B32A23C1612}">
-  <dimension ref="A1:A101"/>
+  <dimension ref="A1:A131"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -8316,6 +9433,156 @@
         <v>1085</v>
       </c>
     </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>1284</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8323,7 +9590,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20836306-9997-450D-A55C-BA5D93912EB9}">
-  <dimension ref="A1:A112"/>
+  <dimension ref="A1:A142"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
@@ -8884,9 +10151,159 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+    <row r="112" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="8" t="s">
         <v>1056</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>1314</v>
       </c>
     </row>
   </sheetData>
@@ -8896,7 +10313,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3999BA3D-14F7-4974-A4C1-C319E42C52A3}">
-  <dimension ref="A1:A98"/>
+  <dimension ref="A1:A128"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -9384,9 +10801,159 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+    <row r="98" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="8" t="s">
         <v>1023</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>1344</v>
       </c>
     </row>
   </sheetData>
@@ -9396,7 +10963,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C323B3F7-4FF2-40F4-B949-CB50AFBFD4BF}">
-  <dimension ref="A1:A80"/>
+  <dimension ref="A1:A110"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -9794,9 +11361,159 @@
         <v>995</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="80" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="8" t="s">
         <v>996</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>1374</v>
       </c>
     </row>
   </sheetData>
@@ -9806,7 +11523,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71AA6F2-96E2-41C0-846E-4C4726501A64}">
-  <dimension ref="A1:A109"/>
+  <dimension ref="A1:A139"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -10349,9 +12066,159 @@
         <v>975</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+    <row r="109" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="8" t="s">
         <v>976</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>1404</v>
       </c>
     </row>
   </sheetData>

--- a/Input/search_query.xlsx
+++ b/Input/search_query.xlsx
@@ -8,22 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E09480-52E1-49E9-92FC-95CFDC0EE4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5779F3-B396-4C69-ACEF-528E8295CD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OBC Andolan" sheetId="13" r:id="rId1"/>
-    <sheet name="Devendra Fadnavis" sheetId="1" r:id="rId2"/>
-    <sheet name="Eknath Shinde" sheetId="7" r:id="rId3"/>
-    <sheet name="Prakash Abitkar" sheetId="6" r:id="rId4"/>
-    <sheet name="Ravindra Chavan" sheetId="3" r:id="rId5"/>
-    <sheet name="Ashish Shelar" sheetId="4" r:id="rId6"/>
-    <sheet name="Chandrakant Patil" sheetId="8" r:id="rId7"/>
-    <sheet name="Chandrashekhar Bawankule" sheetId="9" r:id="rId8"/>
-    <sheet name="Shivraj Singh Chauhan" sheetId="12" r:id="rId9"/>
-    <sheet name="Siddharth Shirole" sheetId="5" r:id="rId10"/>
+    <sheet name="Mahsul" sheetId="15" r:id="rId2"/>
+    <sheet name="Panchayat Raj" sheetId="16" r:id="rId3"/>
+    <sheet name="Devendra Fadnavis" sheetId="1" r:id="rId4"/>
+    <sheet name="Eknath Shinde" sheetId="7" r:id="rId5"/>
+    <sheet name="Prakash Abitkar" sheetId="6" r:id="rId6"/>
+    <sheet name="Ravindra Chavan" sheetId="3" r:id="rId7"/>
+    <sheet name="Ashish Shelar" sheetId="4" r:id="rId8"/>
+    <sheet name="Jaykumar Gore" sheetId="14" r:id="rId9"/>
+    <sheet name="Chandrakant Patil" sheetId="8" r:id="rId10"/>
+    <sheet name="Chandrashekhar Bawankule" sheetId="9" r:id="rId11"/>
+    <sheet name="Shivraj Singh Chauhan" sheetId="12" r:id="rId12"/>
+    <sheet name="Siddharth Shirole" sheetId="5" r:id="rId13"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Jaykumar Gore'!$A$1:$A$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Panchayat Raj'!$A$2:$A$16</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="1405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="1505">
   <si>
     <t>Keyword</t>
   </si>
@@ -4260,13 +4267,313 @@
   </si>
   <si>
     <t>शिवराज सिंह चौहान मध्य प्रदेश बजट प्रशंसा बातम्या</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore latest news</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore recent events</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore political news September 2025</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore official updates</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore program yesterday</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore program 18 September 2025</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore events between 12 Sept and 19 Sept 2025</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे ताज्या बातम्या</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे अलीकडील कार्यक्रम</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे राजकीय बातम्या सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे अधिकृत माहिती</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे कालचा कार्यक्रम</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे कार्यक्रम १८ सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे १२ सप्टेंबर ते १९ सप्टेंबर २०२५ मधील कार्यक्रम</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे ताजा खबर</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे के हाल के कार्यक्रम</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे राजनीतिक समाचार सितंबर २०२५</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे आधिकारिक अपडेट</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे का कल का कार्यक्रम</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे का कार्यक्रम १८ सितंबर २०२५</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे के १२ सितंबर से १९ सितंबर २०२५ के बीच के कार्यक्रम</t>
+  </si>
+  <si>
+    <t>What was Jaykumar Gore's schedule yesterday?</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore speech 18 Sept 2025</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore press conference last week</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore Satara district tour</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore video of recent program</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore Facebook live stream</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे यांचे कालचे भाषण</t>
+  </si>
+  <si>
+    <t>आमदार जयकुमार गोरे पत्रकार परिषद</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे सातारा जिल्हा दौरा सप्टेंबर २०२५</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे यांच्या कार्यक्रमाचा व्हिडिओ</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे फेसबुक लाईव्ह</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे का कल का भाषण</t>
+  </si>
+  <si>
+    <t>विधायक जयकुमार गोरे की प्रेस कॉन्फ्रेंस</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे का सतारा जिला दौरा</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे के कार्यक्रम का वीडियो</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे फेसबुक लाइव</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore public address in Satara</t>
+  </si>
+  <si>
+    <t>BJP leader Jaykumar Gore recent speech</t>
+  </si>
+  <si>
+    <t>MLA Jaykumar Gore schedule this week</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore statement on current affairs</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore meeting with party workers</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore September 15 program</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore election campaign</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे यांची जाहीर सभा सातारा</t>
+  </si>
+  <si>
+    <t>भाजप नेते जयकुमार गोरे यांचे अलीकडील भाषण</t>
+  </si>
+  <si>
+    <t>आमदार जयकुमार गोरे यांचे या आठवड्याचे वेळापत्रक</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे यांचे ताज्या घडामोडींवरील विधान</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे यांची कार्यकर्त्यांसोबत बैठक</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे यांचा १५ सप्टेंबरचा कार्यक्रम</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे यांची निवडणूक प्रचार सभा</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे की सार्वजनिक सभा सतारा में</t>
+  </si>
+  <si>
+    <t>भाजपा नेता जयकुमार गोरे का हालिया भाषण</t>
+  </si>
+  <si>
+    <t>विधायक जयकुमार गोरे का इस हफ्ते का शेड्यूल</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे का ताजा घटनाओं पर बयान</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे की पार्टी कार्यकर्ताओं के साथ बैठक</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे का १५ सितंबर का कार्यक्रम</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे का चुनावी अभियान</t>
+  </si>
+  <si>
+    <t>सेवा पंधरवाडा</t>
+  </si>
+  <si>
+    <t>छत्रपती शिवाजी महाराज महाराजस्व अभियानाअंतर्गत “सेवा पंधरवाडा ”</t>
+  </si>
+  <si>
+    <t>महसूल विभाग सेवा पंधरवाडा </t>
+  </si>
+  <si>
+    <t>राष्ट्रनेता ते राष्ट्रपिता सेवा पंधरवाडा</t>
+  </si>
+  <si>
+    <t>पाणंद रस्ते विषयक मोहिम</t>
+  </si>
+  <si>
+    <t>सर्वांसाठी घरे उपक्रम </t>
+  </si>
+  <si>
+    <t>सेवा पंधरवडा लोकार्पण सोहळा </t>
+  </si>
+  <si>
+    <t>छत्रपती शिवाजी महाराज महाराजस्व अभियान </t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे सेवा पंधरवाडा </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सेवा पंधरवाडा </t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे सेवा पंधरवाडा </t>
+  </si>
+  <si>
+    <t>महाराष्ट्र शासन सेवा पंधरवाडा </t>
+  </si>
+  <si>
+    <t>जिल्हाधिकारी कार्यलय सेवा पंधरवाडा </t>
+  </si>
+  <si>
+    <t>१७ ते २२ सप्टेंबर  सेवा पंधरवाडा </t>
+  </si>
+  <si>
+    <t>२३ ते २७ सप्टेंबर सेवा पंधरवाडा </t>
+  </si>
+  <si>
+    <t>२८ सप्टेंबर ते २ ऑक्टोबर सेवा पंधरवाडा </t>
+  </si>
+  <si>
+    <t>17 सप्टेबर ते 2 ऑक्टोबर सेवा पंधरवाडा </t>
+  </si>
+  <si>
+    <t>Jaykumar Gore Panchayat Raj launch Sept 2025 </t>
+  </si>
+  <si>
+    <t>Mukhyamantri Samruddhi Abhiyan floods Solapur</t>
+  </si>
+  <si>
+    <t>Gore Man taluka water project 2025</t>
+  </si>
+  <si>
+    <t>Panchayat Raj workshops Maharashtra Sept</t>
+  </si>
+  <si>
+    <t>Fadnavis Gore rural scheme news</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे पंचायत राज लॉन्च सितंबर 2025</t>
+  </si>
+  <si>
+    <t>समृद्धि अभियान सोलापूर बाढ़ समाचार</t>
+  </si>
+  <si>
+    <t>गोरे माण तालुका जल योजना 2025</t>
+  </si>
+  <si>
+    <t>पंचायत राज कार्यशालाएं महाराष्ट्र सितंबर</t>
+  </si>
+  <si>
+    <t>फडणवीस गोरे ग्रामीण योजना खबर</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे पंचायत राज लॉन्च सप्टेंबर 2025</t>
+  </si>
+  <si>
+    <t>समृद्धी अभियान सोलापूर पूर बातम्या</t>
+  </si>
+  <si>
+    <t>गोरे माण तालुका पाणी योजना 2025</t>
+  </si>
+  <si>
+    <t>पंचायत राज कार्यशाळा महाराष्ट्र सप्टेंबर</t>
+  </si>
+  <si>
+    <t>फडणवीस गोरे ग्राम योजना बातम्या</t>
+  </si>
+  <si>
+    <t>ग्रामसमृद्धी योजना </t>
+  </si>
+  <si>
+    <t>पंचायत राज योजना </t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे </t>
+  </si>
+  <si>
+    <t>Jaykumar gore latest news</t>
+  </si>
+  <si>
+    <t>Jaykumar gore live</t>
+  </si>
+  <si>
+    <t>Panchayatraj yojana </t>
+  </si>
+  <si>
+    <t>Gram samriddhi yojana</t>
+  </si>
+  <si>
+    <t>Gram samrudhhi yojana</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4281,6 +4588,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1B1C1D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -4333,7 +4652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4343,6 +4662,12 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4652,6 +4977,1921 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3999BA3D-14F7-4974-A4C1-C319E42C52A3}">
+  <dimension ref="A1:A128"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="8" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C323B3F7-4FF2-40F4-B949-CB50AFBFD4BF}">
+  <dimension ref="A1:A110"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="8" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71AA6F2-96E2-41C0-846E-4C4726501A64}">
+  <dimension ref="A1:A139"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="8" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D4577D-FE10-42FD-B10A-D28414797A5F}">
   <dimension ref="A1:A79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5057,6 +7297,241 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E6DA9E0-64AA-4554-9BA2-2345EFB46FCC}">
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD679AEC-9472-4E9E-92A1-94D6D51BE9BE}">
+  <dimension ref="A1:A24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A226"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6199,7 +8674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F7DD1D-0DFC-440F-988C-050CA65FFA2F}">
   <dimension ref="A1:A220"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7312,7 +9787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C494B66-AEA5-4CCE-888E-96E7151CA2B5}">
   <dimension ref="A1:I233"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8920,7 +11395,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13BB4D98-1E3A-4E3C-ACBA-9B32A23C1612}">
   <dimension ref="A1:A131"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9588,7 +12063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20836306-9997-450D-A55C-BA5D93912EB9}">
   <dimension ref="A1:A142"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10311,9 +12786,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3999BA3D-14F7-4974-A4C1-C319E42C52A3}">
-  <dimension ref="A1:A128"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF750284-3907-4EA3-9714-0A5BE186DCE1}">
+  <dimension ref="A1:A61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -10323,1902 +12798,302 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>554</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>555</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>556</v>
+      <c r="A4" s="9" t="s">
+        <v>1405</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>557</v>
+      <c r="A5" s="9" t="s">
+        <v>1406</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>558</v>
+      <c r="A6" s="9" t="s">
+        <v>1407</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>559</v>
+      <c r="A7" s="9" t="s">
+        <v>1408</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>560</v>
+      <c r="A8" s="9" t="s">
+        <v>1409</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>561</v>
+      <c r="A9" s="9" t="s">
+        <v>1410</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>562</v>
+      <c r="A10" s="9" t="s">
+        <v>1411</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>563</v>
+      <c r="A11" s="9" t="s">
+        <v>1426</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>564</v>
+      <c r="A12" s="9" t="s">
+        <v>1427</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>565</v>
+      <c r="A13" s="9" t="s">
+        <v>1428</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>566</v>
+      <c r="A14" s="9" t="s">
+        <v>1429</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>567</v>
+      <c r="A15" s="9" t="s">
+        <v>1430</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>568</v>
+      <c r="A16" s="9" t="s">
+        <v>1431</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>569</v>
+      <c r="A17" s="9" t="s">
+        <v>1444</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>570</v>
+      <c r="A18" s="9" t="s">
+        <v>1445</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>571</v>
+      <c r="A19" s="9" t="s">
+        <v>1446</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>572</v>
+      <c r="A20" s="9" t="s">
+        <v>1447</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>573</v>
+      <c r="A21" s="9" t="s">
+        <v>1448</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>574</v>
+      <c r="A22" s="9" t="s">
+        <v>1449</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>575</v>
+      <c r="A23" s="9" t="s">
+        <v>1450</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>576</v>
+      <c r="A24" s="9" t="s">
+        <v>1412</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>577</v>
+      <c r="A25" s="9" t="s">
+        <v>1413</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>578</v>
+      <c r="A26" s="9" t="s">
+        <v>1414</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>579</v>
+      <c r="A27" s="9" t="s">
+        <v>1415</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>580</v>
+      <c r="A28" s="9" t="s">
+        <v>1416</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>581</v>
+      <c r="A29" s="9" t="s">
+        <v>1417</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>582</v>
+      <c r="A30" s="9" t="s">
+        <v>1418</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>583</v>
+      <c r="A31" s="9" t="s">
+        <v>1432</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>584</v>
+      <c r="A32" s="9" t="s">
+        <v>1433</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>585</v>
+      <c r="A33" s="9" t="s">
+        <v>1434</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>586</v>
+      <c r="A34" s="9" t="s">
+        <v>1435</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>587</v>
+      <c r="A35" s="9" t="s">
+        <v>1436</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>588</v>
+      <c r="A36" s="9" t="s">
+        <v>1451</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>589</v>
+      <c r="A37" s="9" t="s">
+        <v>1452</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>590</v>
+      <c r="A38" s="9" t="s">
+        <v>1453</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>591</v>
+      <c r="A39" s="9" t="s">
+        <v>1454</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>592</v>
+      <c r="A40" s="9" t="s">
+        <v>1455</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>593</v>
+      <c r="A41" s="9" t="s">
+        <v>1456</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>594</v>
+      <c r="A42" s="9" t="s">
+        <v>1457</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>595</v>
+      <c r="A43" s="9" t="s">
+        <v>1419</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>596</v>
+      <c r="A44" s="9" t="s">
+        <v>1420</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>597</v>
+      <c r="A45" s="9" t="s">
+        <v>1421</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>598</v>
+      <c r="A46" s="9" t="s">
+        <v>1422</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>599</v>
+      <c r="A47" s="9" t="s">
+        <v>1423</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>600</v>
+      <c r="A48" s="9" t="s">
+        <v>1424</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>601</v>
+      <c r="A49" s="9" t="s">
+        <v>1425</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>602</v>
+      <c r="A50" s="9" t="s">
+        <v>1437</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>603</v>
+      <c r="A51" s="9" t="s">
+        <v>1438</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>604</v>
+      <c r="A52" s="9" t="s">
+        <v>1439</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>605</v>
+      <c r="A53" s="9" t="s">
+        <v>1440</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>606</v>
+      <c r="A54" s="9" t="s">
+        <v>1441</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>607</v>
+      <c r="A55" s="9" t="s">
+        <v>1458</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>608</v>
+      <c r="A56" s="9" t="s">
+        <v>1459</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>609</v>
+      <c r="A57" s="9" t="s">
+        <v>1460</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>610</v>
+      <c r="A58" s="9" t="s">
+        <v>1461</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>611</v>
+      <c r="A59" s="9" t="s">
+        <v>1462</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>612</v>
+      <c r="A60" s="9" t="s">
+        <v>1463</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="8" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C323B3F7-4FF2-40F4-B949-CB50AFBFD4BF}">
-  <dimension ref="A1:A110"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="8" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>1356</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>1361</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>1363</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>1364</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>1367</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>1374</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71AA6F2-96E2-41C0-846E-4C4726501A64}">
-  <dimension ref="A1:A139"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="8" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>1378</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>1379</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>1381</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>1385</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>1386</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>1387</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>1389</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>1390</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>1391</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>1395</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>1396</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>1398</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>1399</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>1401</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>1402</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>1403</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>1404</v>
+      <c r="A61" s="9" t="s">
+        <v>1464</v>
       </c>
     </row>
   </sheetData>

--- a/Input/search_query.xlsx
+++ b/Input/search_query.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itstr\OneDrive\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702E6B2D-772E-4C15-BBD5-AD1BD658FCFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61401704-DF81-43F4-9AFA-B306FEEF19C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="11" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OBC Andolan" sheetId="13" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="1656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="2032">
   <si>
     <t>Keyword</t>
   </si>
@@ -2903,102 +2903,6 @@
     <t>Higher and Technical Education Minister Chandrakant Patil Mahayuti alliance</t>
   </si>
   <si>
-    <t xml:space="preserve">School Education and Marathi Language Minister Ashish Shelar latest news  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">शालेय शिक्षण आणि मराठी भाषा मंत्री आशीष शेलार ताज्या बातम्या  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">शालेय शिक्षण आणि मराठी भाषा मंत्री आशिष शेलार ताज्या बातम्या  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">School Education and Marathi Language Minister Ashish Shelar education reforms 2025  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशीष शेलार शिक्षण सुधारणा 2025  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशिष शेलार शिक्षण सुधारणा 2025  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">School Education and Marathi Language Minister Ashish Shelar Maharashtra school policy  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशीष शेलार महाराष्ट्र शालेय धोरण  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशिष शेलार महाराष्ट्र शालेय धोरण  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">School Education and Marathi Language Minister Ashish Shelar new announcements 2025  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशीष शेलार नवीन घोषणा 2025  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशिष शेलार नवीन घोषणा 2025  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">School Education and Marathi Language Minister Ashish Shelar public interaction  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशीष शेलार जनतेशी संवाद  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशिष शेलार जनतेशी संवाद  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">School Education and Marathi Language Minister Ashish Shelar school infrastructure  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशीष शेलार शालेय पायाभूत सुविधा  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशिष शेलार शालेय पायाभूत सुविधा  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">School Education and Marathi Language Minister Ashish Shelar Marathi language promotion  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशीष शेलार मराठी भाषा प्रोत्साहन  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशिष शेलार मराठी भाषा प्रोत्साहन  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">School Education and Marathi Language Minister Ashish Shelar digital learning initiatives  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशीष शेलार डिजिटल शिक्षण उपक्रम  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशिष शेलार डिजिटल शिक्षण उपक्रम  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">School Education and Marathi Language Minister Ashish Shelar Maharashtra assembly 2025  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशीष शेलार विधानसभा 2025  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशिष शेलार विधानसभा 2025  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">School Education and Marathi Language Minister Ashish Shelar press conference  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशीष शेलार पत्रकार परिषद  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशिष शेलार पत्रकार परिषद  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">School Education and Marathi Language Minister Ashish Shelar student welfare schemes  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">आशीष शेलार विद्यार्थी कल्याण योजना  </t>
-  </si>
-  <si>
     <t>आशिष शेलार विद्यार्थी कल्याण योजना</t>
   </si>
   <si>
@@ -3629,24 +3533,12 @@
     <t>आशिष शेलार संजय राऊत आशिया कप टिप्पण्या बातम्या</t>
   </si>
   <si>
-    <t>Ashish Shelar Lalbaugcha Raja auction 2025</t>
-  </si>
-  <si>
-    <t>आशिष शेलार लालबागचा राजा लिलाव २०२५</t>
-  </si>
-  <si>
     <t>आशिष शेलार लालबागचा राजा लिलाव बातम्या</t>
   </si>
   <si>
     <t>आशिष शेलार मराठा आरक्षण स्पष्टीकरण बातम्या</t>
   </si>
   <si>
-    <t>Ashish Shelar Mumbai pothole repairs Ganeshotsav 2025</t>
-  </si>
-  <si>
-    <t>आशिष शेलार मुंबई खड्डे दुरुस्ती गणेशोत्सव २०२५</t>
-  </si>
-  <si>
     <t>आशिष शेलार मुंबई खड्डे दुरुस्ती गणेशोत्सव बातम्या</t>
   </si>
   <si>
@@ -3659,12 +3551,6 @@
     <t>आशिष शेलार आयटी स्टार्टअप उपक्रम बातम्या</t>
   </si>
   <si>
-    <t>Ashish Shelar Ganesh Chaturthi celebrations 2025</t>
-  </si>
-  <si>
-    <t>आशिष शेलार गणेश चतुर्थी उत्सव २०२५</t>
-  </si>
-  <si>
     <t>आशिष शेलार गणेश चतुर्थी उत्सव बातम्या</t>
   </si>
   <si>
@@ -4925,48 +4811,6 @@
     <t>Ravindra Chavan Sangathan Parv review  2025</t>
   </si>
   <si>
-    <t>आशिष शेलार मुंबई इमारत ओसी धोरण  २०२५</t>
-  </si>
-  <si>
-    <t>आशिष शेलार कोळीवाडा विकास योजना  २०२५</t>
-  </si>
-  <si>
-    <t>आशिष शेलार संजय राऊत आशिया कप टिप्पण्या  २०२५</t>
-  </si>
-  <si>
-    <t>आशिष शेलार मराठा आरक्षण स्पष्टीकरण  २०२५</t>
-  </si>
-  <si>
-    <t>आशिष शेलार बीएमसी निवडणूक रणनीती  २०२५</t>
-  </si>
-  <si>
-    <t>आशिष शेलार सांस्कृतिक कार्यक्रम मुंबई  २०२५</t>
-  </si>
-  <si>
-    <t>आशिष शेलार आयटी स्टार्टअप उपक्रम  २०२५</t>
-  </si>
-  <si>
-    <t>Ashish Shelar Mumbai building OC policy  2025</t>
-  </si>
-  <si>
-    <t>Ashish Shelar Koliwada development plan  2025</t>
-  </si>
-  <si>
-    <t>Ashish Shelar Sanjay Raut Asia Cup comments  2025</t>
-  </si>
-  <si>
-    <t>Ashish Shelar Maratha quota clarification  2025</t>
-  </si>
-  <si>
-    <t>Ashish Shelar BMC election strategy  2025</t>
-  </si>
-  <si>
-    <t>Ashish Shelar cultural events Mumbai  2025</t>
-  </si>
-  <si>
-    <t>Ashish Shelar IT startup initiatives  2025</t>
-  </si>
-  <si>
     <t>Jaykumar Gore political news  2025</t>
   </si>
   <si>
@@ -5022,6 +4866,1290 @@
   </si>
   <si>
     <t>चंद्रशेखर बावनकुळे मराठा आरक्षण समित्या  २०२५</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर आरोग्य विभाग योजना</t>
+  </si>
+  <si>
+    <t>आरोग्यमंत्री प्रकाश अबिटकर</t>
+  </si>
+  <si>
+    <t>prakash abitkar health minister</t>
+  </si>
+  <si>
+    <t>प्रकाश अबिटकर मराठी बातम्या</t>
+  </si>
+  <si>
+    <t>prakash abitkar health policy</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar Maharashtra Health Minister</t>
+  </si>
+  <si>
+    <t>आरोग्यमंत्री प्रकाश आबिटकर मराठी बातम्या</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar Maharashtra assembly health updates</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर कोल्हापूर शेती बातम्या</t>
+  </si>
+  <si>
+    <t>आरोग्यमंत्री प्रकाश आबिटकर विधानसभा 2025</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर मराठी ताज्या आरोग्य घोषणा</t>
+  </si>
+  <si>
+    <t>prakash abitkar health infrastructure development</t>
+  </si>
+  <si>
+    <t>School Education and Marathi Language Minister Ashish Shelar latest news</t>
+  </si>
+  <si>
+    <t>शालेय शिक्षण आणि मराठी भाषा मंत्री आशीष शेलार ताज्या बातम्या</t>
+  </si>
+  <si>
+    <t>शालेय शिक्षण आणि मराठी भाषा मंत्री आशिष शेलार ताज्या बातम्या</t>
+  </si>
+  <si>
+    <t>School Education and Marathi Language Minister Ashish Shelar education reforms</t>
+  </si>
+  <si>
+    <t>आशीष शेलार शिक्षण सुधारणा</t>
+  </si>
+  <si>
+    <t>आशिष शेलार शिक्षण सुधारणा</t>
+  </si>
+  <si>
+    <t>School Education and Marathi Language Minister Ashish Shelar Maharashtra school policy</t>
+  </si>
+  <si>
+    <t>आशीष शेलार महाराष्ट्र शालेय धोरण</t>
+  </si>
+  <si>
+    <t>आशिष शेलार महाराष्ट्र शालेय धोरण</t>
+  </si>
+  <si>
+    <t>School Education and Marathi Language Minister Ashish Shelar new announcements</t>
+  </si>
+  <si>
+    <t>आशीष शेलार नवीन घोषणा</t>
+  </si>
+  <si>
+    <t>आशिष शेलार नवीन घोषणा</t>
+  </si>
+  <si>
+    <t>School Education and Marathi Language Minister Ashish Shelar public interaction</t>
+  </si>
+  <si>
+    <t>आशिष शेलार जनतेशी संवाद</t>
+  </si>
+  <si>
+    <t>School Education and Marathi Language Minister Ashish Shelar school infrastructure</t>
+  </si>
+  <si>
+    <t>आशीष शेलार शालेय पायाभूत सुविधा</t>
+  </si>
+  <si>
+    <t>आशिष शेलार शालेय पायाभूत सुविधा</t>
+  </si>
+  <si>
+    <t>School Education and Marathi Language Minister Ashish Shelar Marathi language promotion</t>
+  </si>
+  <si>
+    <t>आशीष शेलार मराठी भाषा प्रोत्साहन</t>
+  </si>
+  <si>
+    <t>आशिष शेलार मराठी भाषा प्रोत्साहन</t>
+  </si>
+  <si>
+    <t>School Education and Marathi Language Minister Ashish Shelar digital learning initiatives</t>
+  </si>
+  <si>
+    <t>आशीष शेलार डिजिटल शिक्षण उपक्रम</t>
+  </si>
+  <si>
+    <t>आशिष शेलार डिजिटल शिक्षण उपक्रम</t>
+  </si>
+  <si>
+    <t>School Education and Marathi Language Minister Ashish Shelar Maharashtra assembly</t>
+  </si>
+  <si>
+    <t>आशीष शेलार विधानसभा</t>
+  </si>
+  <si>
+    <t>आशिष शेलार विधानसभा</t>
+  </si>
+  <si>
+    <t>School Education and Marathi Language Minister Ashish Shelar press conference</t>
+  </si>
+  <si>
+    <t>आशिष शेलार पत्रकार परिषद</t>
+  </si>
+  <si>
+    <t>School Education and Marathi Language Minister Ashish Shelar student welfare schemes</t>
+  </si>
+  <si>
+    <t>आशीष शेलार विद्यार्थी कल्याण योजना</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Mumbai building OC policy</t>
+  </si>
+  <si>
+    <t>आशिष शेलार मुंबई इमारत ओसी धोरण</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Koliwada development plan</t>
+  </si>
+  <si>
+    <t>आशिष शेलार कोळीवाडा विकास योजना</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Sanjay Raut Asia Cup comments</t>
+  </si>
+  <si>
+    <t>आशिष शेलार संजय राऊत आशिया कप टिप्पण्या</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Lalbaugcha Raja auction</t>
+  </si>
+  <si>
+    <t>आशिष शेलार लालबागचा राजा लिलाव</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Maratha quota clarification</t>
+  </si>
+  <si>
+    <t>आशिष शेलार मराठा आरक्षण स्पष्टीकरण</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Mumbai pothole repairs Ganeshotsav</t>
+  </si>
+  <si>
+    <t>आशिष शेलार मुंबई खड्डे दुरुस्ती गणेशोत्सव</t>
+  </si>
+  <si>
+    <t>Ashish Shelar BMC election strategy</t>
+  </si>
+  <si>
+    <t>आशिष शेलार बीएमसी निवडणूक रणनीती</t>
+  </si>
+  <si>
+    <t>Ashish Shelar cultural events Mumbai</t>
+  </si>
+  <si>
+    <t>आशिष शेलार सांस्कृतिक कार्यक्रम मुंबई</t>
+  </si>
+  <si>
+    <t>Ashish Shelar IT startup initiatives</t>
+  </si>
+  <si>
+    <t>आशिष शेलार आयटी स्टार्टअप उपक्रम</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Ganesh Chaturthi celebrations</t>
+  </si>
+  <si>
+    <t>आशिष शेलार गणेश चतुर्थी उत्सव</t>
+  </si>
+  <si>
+    <t>आशीष शेलार नवीनतम बातम्या</t>
+  </si>
+  <si>
+    <t>आशीष शेलार हिंदी समाचार</t>
+  </si>
+  <si>
+    <t>Cultural Affairs minister Ashish Shelar</t>
+  </si>
+  <si>
+    <t>आशीष शेलार इंग्रजी समाचार</t>
+  </si>
+  <si>
+    <t>आशीष शेलार मोठ्या गणेशमूर्ती विसर्जन आश्वासन</t>
+  </si>
+  <si>
+    <t>आशीष शेलार भाजप अंतर्गत संघर्ष मुंबई</t>
+  </si>
+  <si>
+    <t>Information technology minister Ashish Shelar</t>
+  </si>
+  <si>
+    <t>Ashish Shelar BMC</t>
+  </si>
+  <si>
+    <t>Ashish Shelar BJP</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Mumbai Elections</t>
+  </si>
+  <si>
+    <t>आशीष शेलार महानगरपालिका निवडणुका</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Shiv Sena UBT dilapidated buildings BMC</t>
+  </si>
+  <si>
+    <t>आशीष शेलार मन्नत वन विभाग</t>
+  </si>
+  <si>
+    <t>Ashish Shelar BMC ex-corporators join BJP</t>
+  </si>
+  <si>
+    <t>Maharashtra govt to set up research centre for experimental arts</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Kolhapur film city news</t>
+  </si>
+  <si>
+    <t>आशीष शेलार कोल्हापूर चित्रनगरी बातम्या</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Congress criticism last week</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Thackeray rally criticism 2025</t>
+  </si>
+  <si>
+    <t>आशीष शेलार ठाकरे मोर्चा प्रतिक्रिया</t>
+  </si>
+  <si>
+    <t>Ashish Shelar press conference July</t>
+  </si>
+  <si>
+    <t>Ashish Shelar Pahalgam attack comparison</t>
+  </si>
+  <si>
+    <t>आशीष शेलार मराठी-हिंदी वाद प्रतिक्रिया</t>
+  </si>
+  <si>
+    <t>Ashish Shelar three-language policy defense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">देवेंद्र फडणवीस बातम्या मागील आठवडा </t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र अपडेट्स मागील आठवडा</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस ताज्या अपडेट्स ७ दिवस</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राजकीय बातम्या मागील आठवडा</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सध्याच्या बातम्या</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सरकारच्या बातम्या गेल्या ७ दिवस</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस news</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस latest news</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis news past week</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis recent news</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Maharashtra updates last week</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis latest updates 7 days</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis political news last week</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis current news</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis government news past 7 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ravindra chavan marathi news  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ravindra chavan hindi news  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ravindra chavan बातम्या मराठी  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ravindra chavan बातम्या  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLA ravindra chavan  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLA ravindra chavan latest news </t>
+  </si>
+  <si>
+    <t xml:space="preserve">रवींद्र चव्हाण मराठी बातम्या  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">रविंद्र चव्हाण बातम्या  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">रवींद्र चव्हाण आमदार  </t>
+  </si>
+  <si>
+    <t>prakash abitkar Shivsena leader</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar loan waiver</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर आरोग्य धोरण</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर वारी आरोग्य सेवा</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>latest news about ashish shelar</t>
+  </si>
+  <si>
+    <t>ashish shelar on bmc elections</t>
+  </si>
+  <si>
+    <t>आशीष शेलार मुंबई</t>
+  </si>
+  <si>
+    <t>आशीष शेलार महाराष्ट्र दर्शन प्रदर्शनी</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar historical sword Maharashtra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार ऐतिहासिक तलवार महाराष्ट्र </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar Vidhan Sabha response 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार विधानसभा प्रतिक्रिया 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar Marathi-Hindi dispute response </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार मराठी-हिंदी वाद प्रतिक्रिया 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar employment initiatives Maharashtra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार रोजगार उपक्रम महाराष्ट्र </t>
+  </si>
+  <si>
+    <t>ashish shelar ai policy maharashtra</t>
+  </si>
+  <si>
+    <t>आशीष शेलार रस्ते कामे मुंबई</t>
+  </si>
+  <si>
+    <t>Ashish Shelar speech</t>
+  </si>
+  <si>
+    <t>सांस्कृतिक मंत्री महाराष्ट्र आशिष शेलार</t>
+  </si>
+  <si>
+    <t>माहिती व तंत्रज्ञान मंत्री आशिष शेलार</t>
+  </si>
+  <si>
+    <t>BCCI Treasurer and ashish shelar</t>
+  </si>
+  <si>
+    <t>आशीष शेलार मंत्री</t>
+  </si>
+  <si>
+    <t>आशीष शेलार आमदार</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ashish shelar hindi news  </t>
+  </si>
+  <si>
+    <t>आशीष शेलार ताज्या बातम्या</t>
+  </si>
+  <si>
+    <t>आशीष शेलार बृहन्मुंबई महानगरपालिका</t>
+  </si>
+  <si>
+    <t>आशीष शेलार आजची बातमी</t>
+  </si>
+  <si>
+    <t>Ashish Shelar in Bandra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ashish Shelar news </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार बातम्या </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar latest news </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार नवीनतम बातम्या </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar Marathi news </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार मराठी बातम्या </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar Hindi news </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार हिंदी समाचार </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार इंग्रजी समाचार </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar news 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार बातम्या 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar Marathi news July 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar English news </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar Hindi news July 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar English news July 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar BJP Mumbai activities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार भाजप मुंबई उपक्रम </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar latest news July 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cultural Affairs Minister Ashish Shelar 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Minister Ashish Shelar 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar Bandra West constituency </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार वांद्रे पश्चिम मतदारसंघ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar Rohit Pawar ED investigation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार रोहित पवार ईडी तपास </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar Mumbai BJP meeting July 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish Shelar press conference July 2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार नवीनतम बातम्या  2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार मराठी बातम्या  2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार हिंदी समाचार  2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार इंग्रजी समाचार  2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार मुंबई भाजप बैठक  2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">आशीष शेलार पत्रकार परिषद  2025 </t>
+  </si>
+  <si>
+    <t>latest news about chandrakant patil</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील पुणे</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील भाषण</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील उच्च शिक्षण मंत्री</t>
+  </si>
+  <si>
+    <t xml:space="preserve">चंद्रकांत पाटील ताज्या बातम्या </t>
+  </si>
+  <si>
+    <t>chandrakant patil pune news</t>
+  </si>
+  <si>
+    <t>chandrakant patil education minister</t>
+  </si>
+  <si>
+    <t>chandrakant patil recent updates</t>
+  </si>
+  <si>
+    <t>chandrakant patil political news</t>
+  </si>
+  <si>
+    <t>chandrakant patil latest speech</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील पुणे बातम्या</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील शिक्षण मंत्री</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील नवीन अपडेट्स</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील राजकीय बातम्या</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील अलीकडील भाषण</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील मंत्री</t>
+  </si>
+  <si>
+    <t>चंद्रकांत दादा पाटील मंत्री</t>
+  </si>
+  <si>
+    <t>chandrakant patil minister</t>
+  </si>
+  <si>
+    <t>चंद्रकांत पाटील सांगली पालकमंत्री</t>
+  </si>
+  <si>
+    <t xml:space="preserve">उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील </t>
+  </si>
+  <si>
+    <t>संसदीय कार्यमंत्री चंद्रकांत पाटील</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule latest activities 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे ताज्या उपक्रम 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Nagpur guardian minister activities 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule farm loan waiver committee 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे शेतकरी कर्जमाफी समिती 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule new policy announcements 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Maharashtra BJP activities 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे महाराष्ट्र विधानसभा 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule tehsildar suspension Nagpur 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे तहसीलदार निलंबन नागपूर 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule unauthorized churches Nandurbar 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे नंदुरबार अनधिकृत चर्च 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule local elections Mahayuti 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे स्थानिक निवडणूक महायुती 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Sindhudurg Janata Darbar 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे सिंधुदुर्ग जनता दरबार 2025</t>
+  </si>
+  <si>
+    <t>Revenue Minister Chandrashekhar Bawankule  2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Marathi news  2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Hindi news  2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Nagpur news  2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Nagpur constituency work  2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Nagpur visits  2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule revenue minister activities  2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule revenue department updates  2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule BJP State President  2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Janata Darbar Nagpur  2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule public interaction  2025</t>
+  </si>
+  <si>
+    <t>महसूल मंत्री चंद्रशेखर बावनकुळे  2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे मराठी बातम्या  2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे हिंदी बातम्या  2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे नागपूर ताज्या बातम्या  2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे नागपूर पालकमंत्री उपक्रम  2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे नागपूर मतदारसंघ कार्य  2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे नागपूर दौरा  2025</t>
+  </si>
+  <si>
+    <t>महसूल मंत्री चंद्रशेखर बावनकुळे उपक्रम  2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे महसूल मंत्रालय अपडेट्स  2025</t>
+  </si>
+  <si>
+    <t>महसूल मंत्री चंद्रशेखर बावनकुळे नवीन घोषणा  2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे भाजप प्रदेशाध्यक्ष  2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे महाराष्ट्र भाजप उपक्रम  2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे जनता दरबार नागपूर  2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे जनतेशी संवाद  2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Mumbai BJP office public interaction 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे मुंबई भाजपा कार्यालय जनसंवाद 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Pune MIDC land allocation 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे पुणे एमआयडीसी जमीन वाटप 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Maratha reservation statement 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे मराठा आरक्षण विधान 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule revenue week outcomes 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे महसूल सप्ताह परिणाम 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Nagpur public grievance redressal 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे नागपूर जनतेच्या तक्रार निवारण 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule BJP membership drive Nagpur 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे भाजपा सदस्यता अभियान नागपूर 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Amravati guardian minister review 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे अमरावती पालकमंत्री आढावा 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Pune agricultural corporation workers meeting 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे पुणे शेती महामंडळ कामगार बैठक 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Maharashtra local body election strategy 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे महाराष्ट्र स्थानिक निवडणूक रणनीती 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Devendra Fadnavis Mumbai meeting 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे देवेंद्र फडणवीस मुंबई बैठक 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule rural revenue officer initiatives 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे ग्रामीण महसूल अधिकारी उपक्रम 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule Nagpur village outreach program 2025</t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे नागपूर गाव संनाद कार्यक्रम 2025</t>
+  </si>
+  <si>
+    <t>Chandrashekhar Bawankule revenue department digital reforms 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">महसूल मंत्री चंद्रशेखर बावनकुळे   </t>
+  </si>
+  <si>
+    <t>चंद्रशेखर बावनकुळे महसूल मंत्रालय डिजिटल सुधारणा 2025</t>
+  </si>
+  <si>
+    <t>Bawankule farm loan waiver committee formed</t>
+  </si>
+  <si>
+    <t>chandrashekhar bawankule illegal plotting</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan news</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan latest news</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Union Minister news</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान केंद्रीय मंत्री समाचार</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan BJP news</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान भाजपा समाचार</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan politics news</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान राजनीति समाचार</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Bhopal news</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान भोपाल समाचार</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan speech</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan reaction</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान प्रतिक्रिया</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan opposition</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान विपक्ष</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan election</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan campaign</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान प्रचार</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan rally</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान सभा</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan political decision</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान राजनीतिक निर्णय</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Kamal Nath</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान कमल नाथ</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Legislative Assembly</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान विधान सभा</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan press conference</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan government</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान सरकार</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan new project</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान नया प्रकल्प</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan statement</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan politics</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Madhya Pradesh election</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान मध्य प्रदेश चुनाव</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan opposition statement</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान विपक्ष पर बयान</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan new scheme</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान नई योजना</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan government scheme</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Mohan Yadav government</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान मोहन यादव सरकार</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan public rally</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Madhya Pradesh BJP</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान मध्य प्रदेश भाजपा</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan vs Kamal Nath</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान बनाम कमल नाथ</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan alliance strategy</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान गठबंधन रणनीति</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan speech highlights</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान भाषण की मुख्य बातें</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan development project</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान विकास प्रकल्प</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan infrastructure policy</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान बुनियादी ढांचा नीति</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan central government coordination</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान केंद्र सरकार समन्वय</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Modi government</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan on Rahul Gandhi</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान राहुल गांधी पर</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan controversy</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान विवाद</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Agriculture Ministry 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान कृषि मंत्रालय 2025</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Ladli Behna Yojana</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान लाडली बहना योजना</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Kisan Samman Nidhi 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान किसान सम्मान निधि 2025</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Bhopal voter list controversy 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान भोपाल मतदाता सूची विवाद 2025</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Kamal Nath remarks</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान कमल नाथ बयान</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Madhya Pradesh Radio Festival</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान मध्य प्रदेश रेडियो फेस्टिवल</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Vyapam scam controversy</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान व्यापम घोटाला विवाद</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Budhni constituency</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान बुढ़नी निर्वाचन क्षेत्र</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan BJP Madhya Pradesh leadership</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान भाजपा मध्य प्रदेश नेतृत्व</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan infrastructure policies Madhya Pradesh</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान मध्य प्रदेश बुनियादी ढांचा नीतियां</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan 2013 election affidavit controversy</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान 2013 चुनाव हलफनामा विवाद</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan drought management Madhya Pradesh</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान मध्य प्रदेश सूखा प्रबंधन</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan RSS background</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान आरएसएस पृष्ठभूमि</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Bhopal</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan this week events 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान इस सप्ताह की घटनाएं 2025</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Kisan Mahotsav 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान किसान महोत्सव 2025</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan environmental initiative 2025</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan rural development initiatives</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान ग्रामीण विकास पहल</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan urban infrastructure projects</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान शहरी बुनियादी ढांचा परियोजनाएं</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan economic policies Madhya Pradesh</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान मध्य प्रदेश आर्थिक नीतियां</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan social welfare schemes 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान सामाजिक कल्याण योजनाएं 2025</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan political activities 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान जुलाई 2025 राजनीतिक गतिविधियां</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan public engagements 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान सार्वजनिक सहभाग 2025</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan Madhya Pradesh governance 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान मध्य प्रदेश शासन 2025</t>
+  </si>
+  <si>
+    <t>Shivraj Singh Chauhan policy decisions 2025</t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान नीति निर्णय 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan Union Minister activities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान केंद्रीय मंत्री उपक्रम </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान केंद्रीय मंत्री गतिविधियां </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan BJP activities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान भाजपा उपक्रम </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान भाजपा गतिविधियां </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan Bhopal activities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान भोपाल उपक्रम </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान भोपाल गतिविधियां </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan Kisan Mahotsav </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान किसान महोत्सव </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan One Nation One Election </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान एक देश एक निवडणूक </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान एक राष्ट्र एक चुनाव </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan Donald Trump tariffs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान डोनाल्ड ट्रम्प शुल्क </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान डोनाल्ड ट्रम्प टैरिफ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan agriculture policy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान कृषि धोरण </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान कृषि नीति </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan rural development initiatives </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान ग्रामीण विकास उपक्रम </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान ग्रामीण विकास पहल </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan farmers welfare schemes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान शेतकरी कल्याण योजना </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान किसान कल्याण योजनाएं </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan Vidisha constituency </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान विदिशा मतदारसंघ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान विदिशा निर्वाचन क्षेत्र </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan trade industry meeting Delhi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान व्यापार उद्योग बैठक दिल्ली </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan Congress criticism </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान काँग्रेस टीका </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान कांग्रेस आलोचना </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan Madhya Pradesh BJP activities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान मध्य प्रदेश भाजपा उपक्रम </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान मध्य प्रदेश भाजपा गतिविधियां </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan Kisan Samman Nidhi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान किसान सम्मान निधि </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan agricultural exports </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान कृषि निर्यात </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan public rally </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान सार्वजनिक सभा </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chouhan policy decisions </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान धोरण निर्णय </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान नीति निर्णय </t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान पर्यावरण पहल 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chauhan Agriculture Ministry portfolio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान कृषि मंत्रालय पोर्टफोलियो </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivraj Singh Chauhan Chief Minister tenure </t>
+  </si>
+  <si>
+    <t xml:space="preserve">शिवराज सिंह चौहान मुख्यमंत्री कार्यकाल </t>
+  </si>
+  <si>
+    <t>शिवराज सिंह चौहान  कांग्रेस सरकार पतन</t>
   </si>
 </sst>
 </file>
@@ -5107,7 +6235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -5141,6 +6269,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5431,17 +6560,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1070</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1068</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>1069</v>
+        <v>1037</v>
       </c>
     </row>
   </sheetData>
@@ -5451,7 +6580,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20836306-9997-450D-A55C-BA5D93912EB9}">
-  <dimension ref="A1:A142"/>
+  <dimension ref="A1:A222"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
@@ -5852,319 +6981,719 @@
         <v>553</v>
       </c>
     </row>
-    <row r="80" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="3" t="s">
-        <v>949</v>
+    <row r="80" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>1616</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>950</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>951</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>952</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>953</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>954</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>955</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>956</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>957</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>958</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>959</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>960</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>961</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>962</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>963</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>964</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>965</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>966</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>967</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>968</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>969</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>970</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>971</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>972</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>973</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>974</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>975</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>976</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>977</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>978</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>979</v>
+        <v>949</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="8" t="s">
-        <v>981</v>
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="17" t="s">
+        <v>1647</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>1630</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>1623</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>1188</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>1631</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>1624</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>1189</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>1632</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>1625</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>1190</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>1191</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>1192</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>1193</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>1633</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>1626</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1194</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>1195</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>1196</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>1197</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>1634</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>1627</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>1198</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>1635</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>1628</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>1199</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>1636</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>1629</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>1200</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>1201</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>1202</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>1203</v>
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>1718</v>
       </c>
     </row>
   </sheetData>
@@ -6184,272 +7713,272 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1246</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1247</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>1219</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>1220</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>1637</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>1221</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>1222</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>1638</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>1223</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>1231</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>1232</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>1233</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>1234</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>1235</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>1236</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>1248</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>1249</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>1250</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>1251</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>1252</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>1639</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>1253</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>1224</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>1225</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>1641</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>1226</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>1237</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>1238</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>1642</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>1239</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>1240</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>1254</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>1255</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>1256</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>1257</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>1258</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>1643</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>1259</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>1227</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>1228</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>1640</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>1229</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>1230</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>1241</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>1242</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>1243</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>1244</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>1245</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>1260</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>1261</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>1262</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>1263</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>1264</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
-        <v>1265</v>
+        <v>1227</v>
       </c>
     </row>
   </sheetData>
@@ -6459,7 +7988,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3999BA3D-14F7-4974-A4C1-C319E42C52A3}">
-  <dimension ref="A1:A98"/>
+  <dimension ref="A1:A119"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -6817,8 +8346,8 @@
         <v>623</v>
       </c>
     </row>
-    <row r="72" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="s">
+    <row r="72" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="17" t="s">
         <v>922</v>
       </c>
     </row>
@@ -6947,9 +8476,114 @@
         <v>947</v>
       </c>
     </row>
-    <row r="98" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="8" t="s">
+    <row r="98" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="17" t="s">
         <v>948</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>1796</v>
       </c>
     </row>
   </sheetData>
@@ -6959,7 +8593,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C323B3F7-4FF2-40F4-B949-CB50AFBFD4BF}">
-  <dimension ref="A1:A92"/>
+  <dimension ref="A1:A162"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -7364,62 +8998,412 @@
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>1204</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>1652</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>1205</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>1206</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>1653</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>1207</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>1208</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>1654</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>1209</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>1210</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>1655</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>1211</v>
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>1866</v>
       </c>
     </row>
   </sheetData>
@@ -7429,7 +9413,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71AA6F2-96E2-41C0-846E-4C4726501A64}">
-  <dimension ref="A1:A124"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -7979,77 +9963,902 @@
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>1648</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>1644</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>1212</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>1213</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>1214</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>1215</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>1649</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>1645</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>1216</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>1650</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>1646</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>1217</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>1651</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>1647</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>1218</v>
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>2025</v>
       </c>
     </row>
   </sheetData>
@@ -8474,302 +11283,302 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>1466</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>1467</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>1468</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>1469</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>1470</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>1471</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>1472</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>1473</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>1474</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>1475</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>1476</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>1477</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>1478</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>1479</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>1480</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="16" t="s">
-        <v>1481</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>1482</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>1483</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
-        <v>1484</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>1485</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
-        <v>1486</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="16" t="s">
-        <v>1487</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="16" t="s">
-        <v>1488</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="16" t="s">
-        <v>1489</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="16" t="s">
-        <v>1490</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="16" t="s">
-        <v>1491</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="16" t="s">
-        <v>1492</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="16" t="s">
-        <v>1493</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="16" t="s">
-        <v>1494</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="16" t="s">
-        <v>1495</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="16" t="s">
-        <v>1496</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="16" t="s">
-        <v>1497</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="16" t="s">
-        <v>1498</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="16" t="s">
-        <v>1499</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="16" t="s">
-        <v>1500</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="16" t="s">
-        <v>1501</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="16" t="s">
-        <v>1502</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="16" t="s">
-        <v>1503</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="16" t="s">
-        <v>1504</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="16" t="s">
-        <v>1505</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="16" t="s">
-        <v>1506</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="16" t="s">
-        <v>1507</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="16" t="s">
-        <v>1508</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="16" t="s">
-        <v>1509</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="16" t="s">
-        <v>1510</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="16" t="s">
-        <v>1511</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" s="16" t="s">
-        <v>1512</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="16" t="s">
-        <v>1513</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="16" t="s">
-        <v>1514</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="16" t="s">
-        <v>1515</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="16" t="s">
-        <v>1516</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="16" t="s">
-        <v>1517</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="16" t="s">
-        <v>1518</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="16" t="s">
-        <v>1519</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" s="16" t="s">
-        <v>1520</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" s="16" t="s">
-        <v>1521</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" s="16" t="s">
-        <v>1522</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
-        <v>1523</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" s="16" t="s">
-        <v>1524</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" s="16" t="s">
-        <v>1525</v>
+        <v>1487</v>
       </c>
     </row>
   </sheetData>
@@ -8792,802 +11601,802 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>1465</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>1306</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>1307</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
-        <v>1308</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
-        <v>1309</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
-        <v>1310</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
-        <v>1311</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
-        <v>1312</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
-        <v>1313</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
-        <v>1314</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
-        <v>1315</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
-        <v>1316</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
-        <v>1317</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
-        <v>1318</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
-        <v>1319</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
-        <v>1320</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
-        <v>1321</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>1322</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>1323</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
-        <v>1324</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
-        <v>1325</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
-        <v>1326</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
-        <v>1327</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
-        <v>1328</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="12" t="s">
-        <v>1329</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
-        <v>1330</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
-        <v>1331</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
-        <v>1332</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
-        <v>1333</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
-        <v>1334</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
-        <v>1335</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
-        <v>1336</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
-        <v>1337</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
-        <v>1338</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
-        <v>1339</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="12" t="s">
-        <v>1340</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>1341</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
-        <v>1342</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
-        <v>1343</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>1344</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
-        <v>1345</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="12" t="s">
-        <v>1346</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="12" t="s">
-        <v>1347</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="12" t="s">
-        <v>1348</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="12" t="s">
-        <v>1349</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="12" t="s">
-        <v>1350</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" s="12" t="s">
-        <v>1351</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="12" t="s">
-        <v>1352</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="12" t="s">
-        <v>1353</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="12" t="s">
-        <v>1354</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="12" t="s">
-        <v>1355</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="12" t="s">
-        <v>1356</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="12" t="s">
-        <v>1357</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="12" t="s">
-        <v>1358</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" s="12" t="s">
-        <v>1359</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" s="12" t="s">
-        <v>1360</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" s="12" t="s">
-        <v>1361</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" s="12" t="s">
-        <v>1362</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" s="12" t="s">
-        <v>1363</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" s="12" t="s">
-        <v>1364</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" s="12" t="s">
-        <v>1365</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="12" t="s">
-        <v>1366</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" s="12" t="s">
-        <v>1367</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="12" t="s">
-        <v>1368</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" s="12" t="s">
-        <v>1369</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" s="12" t="s">
-        <v>1370</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" s="12" t="s">
-        <v>1371</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" s="12" t="s">
-        <v>1372</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" s="12" t="s">
-        <v>1373</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" s="12" t="s">
-        <v>1374</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" s="12" t="s">
-        <v>1375</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" s="12" t="s">
-        <v>1376</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" s="12" t="s">
-        <v>1377</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="13" t="s">
-        <v>1378</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="13" t="s">
-        <v>1379</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="77" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="13" t="s">
-        <v>1380</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" s="13" t="s">
-        <v>1381</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="79" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" s="13" t="s">
-        <v>1382</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" s="13" t="s">
-        <v>1383</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="81" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A81" s="13" t="s">
-        <v>1384</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="13" t="s">
-        <v>1385</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="83" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" s="13" t="s">
-        <v>1386</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" s="13" t="s">
-        <v>1387</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="85" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A85" s="13" t="s">
-        <v>1388</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" s="13" t="s">
-        <v>1389</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="87" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A87" s="13" t="s">
-        <v>1390</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="88" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="13" t="s">
-        <v>1391</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="89" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" s="13" t="s">
-        <v>1392</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" s="13" t="s">
-        <v>1393</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="91" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A91" s="13" t="s">
-        <v>1394</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" s="13" t="s">
-        <v>1395</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="93" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="13" t="s">
-        <v>1396</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="13" t="s">
-        <v>1397</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" s="13" t="s">
-        <v>1398</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" s="13" t="s">
-        <v>1399</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="97" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" s="13" t="s">
-        <v>1400</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" s="13" t="s">
-        <v>1401</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="99" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="13" t="s">
-        <v>1402</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="100" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A100" s="13" t="s">
-        <v>1403</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" s="13" t="s">
-        <v>1404</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102" s="13" t="s">
-        <v>1405</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" s="13" t="s">
-        <v>1406</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104" s="13" t="s">
-        <v>1407</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105" s="13" t="s">
-        <v>1408</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106" s="13" t="s">
-        <v>1409</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107" s="13" t="s">
-        <v>1410</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108" s="13" t="s">
-        <v>1411</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109" s="13" t="s">
-        <v>1412</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110" s="13" t="s">
-        <v>1413</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111" s="13" t="s">
-        <v>1414</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112" s="13" t="s">
-        <v>1415</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113" s="13" t="s">
-        <v>1416</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114" s="13" t="s">
-        <v>1417</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115" s="13" t="s">
-        <v>1418</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116" s="13" t="s">
-        <v>1419</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117" s="13" t="s">
-        <v>1420</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118" s="13" t="s">
-        <v>1421</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119" s="13" t="s">
-        <v>1422</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120" s="13" t="s">
-        <v>1423</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121" s="13" t="s">
-        <v>1424</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122" s="13" t="s">
-        <v>1425</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123" s="13" t="s">
-        <v>1426</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124" s="13" t="s">
-        <v>1427</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125" s="13" t="s">
-        <v>1428</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A126" s="13" t="s">
-        <v>1429</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127" s="13" t="s">
-        <v>1430</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A128" s="13" t="s">
-        <v>1431</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="129" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="13" t="s">
-        <v>1432</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A130" s="13" t="s">
-        <v>1433</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="131" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="13" t="s">
-        <v>1434</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A132" s="13" t="s">
-        <v>1435</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="133" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A133" s="13" t="s">
-        <v>1436</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A134" s="13" t="s">
-        <v>1437</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A135" s="13" t="s">
-        <v>1438</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="136" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A136" s="13" t="s">
-        <v>1439</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A137" s="13" t="s">
-        <v>1440</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A138" s="13" t="s">
-        <v>1441</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A139" s="13" t="s">
-        <v>1442</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="140" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A140" s="13" t="s">
-        <v>1443</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A141" s="13" t="s">
-        <v>1444</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A142" s="13" t="s">
-        <v>1445</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A143" s="13" t="s">
-        <v>1446</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A144" s="13" t="s">
-        <v>1447</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A145" s="13" t="s">
-        <v>1448</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A146" s="13" t="s">
-        <v>1449</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A147" s="13" t="s">
-        <v>1450</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A148" s="13" t="s">
-        <v>1451</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A149" s="13" t="s">
-        <v>1452</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A150" s="13" t="s">
-        <v>1453</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A151" s="13" t="s">
-        <v>1454</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A152" s="13" t="s">
-        <v>1455</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A153" s="13" t="s">
-        <v>1456</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A154" s="13" t="s">
-        <v>1457</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A155" s="13" t="s">
-        <v>1458</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="156" spans="1:1" ht="29" x14ac:dyDescent="0.35">
       <c r="A156" s="13" t="s">
-        <v>1459</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A157" s="13" t="s">
-        <v>1460</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A158" s="13" t="s">
-        <v>1461</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A159" s="13" t="s">
-        <v>1462</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A160" s="13" t="s">
-        <v>1463</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161" s="13" t="s">
-        <v>1464</v>
+        <v>1426</v>
       </c>
     </row>
   </sheetData>
@@ -9607,92 +12416,92 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1266</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1267</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>1268</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>1269</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>1270</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>1271</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>1272</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>1273</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>1274</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>1275</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>1276</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>1277</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>1278</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>1268</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>1279</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>1280</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>1281</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>1282</v>
+        <v>1244</v>
       </c>
     </row>
   </sheetData>
@@ -9712,117 +12521,117 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>1283</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
-        <v>1284</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>1285</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>1286</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>1287</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>1288</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>1289</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>1290</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
-        <v>1291</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
-        <v>1292</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
-        <v>1293</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
-        <v>1294</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
-        <v>1295</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="10" t="s">
-        <v>1296</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
-        <v>1297</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>1298</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>1299</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>1300</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>1301</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>1302</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>1303</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>1304</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>1305</v>
+        <v>1267</v>
       </c>
     </row>
   </sheetData>
@@ -9832,7 +12641,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A226"/>
+  <dimension ref="A1:A241"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -10810,162 +13619,237 @@
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>1071</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>1072</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>1073</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>1074</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>1075</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>1076</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>1077</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>1078</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>1079</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>1080</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>1081</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>1082</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>1083</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>1084</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>1085</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>1086</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>1087</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>1088</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>1089</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>1090</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>1091</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>1092</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>1093</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>1094</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>1095</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>1097</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>1098</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>1099</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1100</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>1101</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1102</v>
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>1704</v>
       </c>
     </row>
   </sheetData>
@@ -11723,362 +14607,362 @@
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
-        <v>1038</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
-        <v>1039</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
-        <v>1040</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A152" s="5" t="s">
-        <v>1041</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A153" s="5" t="s">
-        <v>1042</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A154" s="5" t="s">
-        <v>1043</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A155" s="5" t="s">
-        <v>1044</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A156" s="5" t="s">
-        <v>1045</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
-        <v>1046</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A158" s="5" t="s">
-        <v>1047</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
-        <v>1048</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A160" s="5" t="s">
-        <v>1049</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
-        <v>1050</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A162" s="5" t="s">
-        <v>1051</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
-        <v>1052</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A164" s="5" t="s">
-        <v>1053</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A165" s="5" t="s">
-        <v>1054</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
-        <v>1055</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
-        <v>1056</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A168" s="5" t="s">
-        <v>1057</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A169" s="5" t="s">
-        <v>1058</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
-        <v>1059</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
-        <v>1060</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A172" s="5" t="s">
-        <v>1061</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A173" s="5" t="s">
-        <v>1062</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A174" s="5" t="s">
-        <v>1063</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
-        <v>1064</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A176" s="5" t="s">
-        <v>1065</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A177" s="5" t="s">
-        <v>1066</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="178" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A178" s="7" t="s">
-        <v>1067</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A179" s="5" t="s">
-        <v>1103</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A180" s="5" t="s">
-        <v>1104</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A181" s="5" t="s">
-        <v>1105</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A182" s="5" t="s">
-        <v>1106</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A183" s="5" t="s">
-        <v>1107</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A184" s="5" t="s">
-        <v>1108</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A185" s="5" t="s">
-        <v>1109</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A186" s="5" t="s">
-        <v>1110</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A187" s="5" t="s">
-        <v>1111</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A188" s="5" t="s">
-        <v>1112</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A189" s="5" t="s">
-        <v>1113</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A190" s="5" t="s">
-        <v>1114</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A191" s="5" t="s">
-        <v>1115</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A192" s="5" t="s">
-        <v>1116</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A193" s="5" t="s">
-        <v>1117</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A194" s="5" t="s">
-        <v>1118</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A195" s="5" t="s">
-        <v>1119</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A196" s="5" t="s">
-        <v>1120</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A197" s="5" t="s">
-        <v>1121</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A198" s="5" t="s">
-        <v>1122</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A199" s="5" t="s">
-        <v>1123</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A200" s="5" t="s">
-        <v>1124</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A201" s="5" t="s">
-        <v>1125</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A202" s="5" t="s">
-        <v>1126</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A203" s="5" t="s">
-        <v>1127</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A204" s="5" t="s">
-        <v>1128</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
-        <v>1129</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A206" s="5" t="s">
-        <v>1130</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A207" s="5" t="s">
-        <v>1131</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A208" s="5" t="s">
-        <v>1132</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A209" s="5" t="s">
-        <v>1133</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A210" s="5" t="s">
-        <v>1134</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A211" s="5" t="s">
-        <v>1135</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A212" s="5" t="s">
-        <v>1136</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A213" s="5" t="s">
-        <v>1137</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A214" s="5" t="s">
-        <v>1138</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A215" s="5" t="s">
-        <v>1139</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A216" s="5" t="s">
-        <v>1140</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A217" s="5" t="s">
-        <v>1141</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A218" s="5" t="s">
-        <v>1142</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A219" s="5" t="s">
-        <v>1143</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A220" s="5" t="s">
-        <v>1144</v>
+        <v>1112</v>
       </c>
     </row>
   </sheetData>
@@ -12088,1605 +14972,1685 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C494B66-AEA5-4CCE-888E-96E7151CA2B5}">
-  <dimension ref="A1:I233"/>
+  <dimension ref="A1:H249"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
+      <c r="F3" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="G4" t="s">
+      <c r="F4" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F5" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="G6" t="s">
+      <c r="F6" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>33</v>
       </c>
-      <c r="G7" t="s">
+      <c r="F7" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="G8" t="s">
+      <c r="F8" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="G9" t="s">
+      <c r="F9" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>36</v>
       </c>
-      <c r="G10" t="s">
+      <c r="F10" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="G11" t="s">
+      <c r="F11" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>38</v>
       </c>
-      <c r="G12" t="s">
+      <c r="F12" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="G13" t="s">
+      <c r="F13" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="G14" t="s">
+      <c r="F14" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="G15" t="s">
+      <c r="F15" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="G16" t="s">
+      <c r="F16" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="G17" t="s">
+      <c r="F17" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>44</v>
       </c>
-      <c r="G18" t="s">
+      <c r="F18" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>45</v>
       </c>
-      <c r="G19" t="s">
+      <c r="F19" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
-      <c r="G20" t="s">
+      <c r="F20" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>47</v>
       </c>
-      <c r="G21" t="s">
+      <c r="F21" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>48</v>
       </c>
-      <c r="G22" t="s">
+      <c r="F22" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>49</v>
       </c>
-      <c r="G23" t="s">
+      <c r="F23" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>50</v>
       </c>
-      <c r="G24" t="s">
+      <c r="F24" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>51</v>
       </c>
-      <c r="G25" t="s">
+      <c r="F25" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>52</v>
       </c>
-      <c r="G26" t="s">
+      <c r="F26" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>53</v>
       </c>
-      <c r="G27" t="s">
+      <c r="F27" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>54</v>
       </c>
-      <c r="G28" t="s">
+      <c r="F28" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>55</v>
       </c>
-      <c r="G29" t="s">
+      <c r="F29" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>56</v>
       </c>
-      <c r="G30" t="s">
+      <c r="F30" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>57</v>
       </c>
-      <c r="G31" t="s">
+      <c r="F31" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>58</v>
       </c>
-      <c r="G32" t="s">
+      <c r="F32" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>59</v>
       </c>
-      <c r="G33" t="s">
+      <c r="F33" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>60</v>
       </c>
-      <c r="G34" t="s">
+      <c r="F34" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>61</v>
       </c>
-      <c r="G35" t="s">
+      <c r="F35" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>62</v>
       </c>
-      <c r="G36" t="s">
+      <c r="F36" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>63</v>
       </c>
-      <c r="G37" t="s">
+      <c r="F37" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>64</v>
       </c>
-      <c r="G38" t="s">
+      <c r="F38" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>65</v>
       </c>
-      <c r="G39" t="s">
+      <c r="F39" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>66</v>
       </c>
-      <c r="G40" t="s">
+      <c r="F40" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>67</v>
       </c>
-      <c r="G41" t="s">
+      <c r="F41" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>68</v>
       </c>
-      <c r="G42" t="s">
+      <c r="F42" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>69</v>
       </c>
-      <c r="G43" t="s">
+      <c r="F43" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>70</v>
       </c>
-      <c r="G44" t="s">
+      <c r="F44" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>71</v>
       </c>
-      <c r="G45" t="s">
+      <c r="F45" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>72</v>
       </c>
-      <c r="G46" t="s">
+      <c r="F46" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>827</v>
       </c>
-      <c r="G47" t="s">
+      <c r="F47" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>828</v>
       </c>
-      <c r="G48" t="s">
+      <c r="F48" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>829</v>
       </c>
-      <c r="G49" t="s">
+      <c r="F49" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>830</v>
       </c>
-      <c r="G50" t="s">
+      <c r="F50" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>831</v>
       </c>
-      <c r="G51" t="s">
+      <c r="F51" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>832</v>
       </c>
-      <c r="G52" t="s">
+      <c r="F52" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>833</v>
       </c>
-      <c r="G53" t="s">
+      <c r="F53" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>834</v>
       </c>
-      <c r="G54" t="s">
+      <c r="F54" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>835</v>
       </c>
-      <c r="G55" t="s">
+      <c r="F55" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>836</v>
       </c>
-      <c r="G56" t="s">
+      <c r="F56" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>837</v>
       </c>
-      <c r="G57" t="s">
+      <c r="F57" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>838</v>
       </c>
-      <c r="G58" t="s">
+      <c r="F58" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>1565</v>
-      </c>
-      <c r="G59" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F59" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>1526</v>
-      </c>
-      <c r="G60" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F60" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>1566</v>
-      </c>
-      <c r="G61" t="s">
+        <v>1528</v>
+      </c>
+      <c r="F61" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>1527</v>
-      </c>
-      <c r="G62" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F62" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>839</v>
       </c>
-      <c r="G63" t="s">
+      <c r="F63" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>840</v>
       </c>
-      <c r="G64" t="s">
+      <c r="F64" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>1567</v>
-      </c>
-      <c r="G65" t="s">
+        <v>1529</v>
+      </c>
+      <c r="F65" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>1528</v>
-      </c>
-      <c r="G66" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F66" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>841</v>
       </c>
-      <c r="G67" t="s">
+      <c r="F67" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>842</v>
       </c>
-      <c r="G68" t="s">
+      <c r="F68" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>843</v>
       </c>
-      <c r="G69" t="s">
+      <c r="F69" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>844</v>
       </c>
-      <c r="G70" t="s">
+      <c r="F70" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>845</v>
       </c>
-      <c r="G71" t="s">
+      <c r="F71" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>846</v>
       </c>
-      <c r="G72" t="s">
+      <c r="F72" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>847</v>
       </c>
-      <c r="G73" t="s">
+      <c r="F73" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>848</v>
       </c>
-      <c r="G74" t="s">
+      <c r="F74" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>849</v>
       </c>
-      <c r="G75" t="s">
+      <c r="F75" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>850</v>
       </c>
-      <c r="G76" t="s">
+      <c r="F76" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>851</v>
       </c>
-      <c r="G77" t="s">
+      <c r="F77" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>852</v>
       </c>
-      <c r="G78" t="s">
+      <c r="F78" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>853</v>
       </c>
-      <c r="G79" t="s">
+      <c r="F79" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>854</v>
       </c>
-      <c r="G80" t="s">
+      <c r="F80" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>855</v>
       </c>
-      <c r="G81" t="s">
+      <c r="F81" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>856</v>
       </c>
-      <c r="G82" t="s">
+      <c r="F82" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>857</v>
       </c>
-      <c r="G83" t="s">
+      <c r="F83" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>858</v>
       </c>
-      <c r="G84" t="s">
+      <c r="F84" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>859</v>
       </c>
-      <c r="G85" t="s">
+      <c r="F85" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>860</v>
       </c>
-      <c r="G86" t="s">
+      <c r="F86" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>861</v>
       </c>
-      <c r="G87" t="s">
+      <c r="F87" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>862</v>
       </c>
-      <c r="G88" t="s">
+      <c r="F88" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>863</v>
       </c>
-      <c r="G89" t="s">
+      <c r="F89" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>864</v>
       </c>
-      <c r="G90" t="s">
+      <c r="F90" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>865</v>
       </c>
-      <c r="G91" t="s">
+      <c r="F91" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>866</v>
       </c>
-      <c r="G92" t="s">
+      <c r="F92" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>867</v>
       </c>
-      <c r="G93" t="s">
+      <c r="F93" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>1568</v>
-      </c>
-      <c r="G94" t="s">
+        <v>1530</v>
+      </c>
+      <c r="F94" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>1529</v>
-      </c>
-      <c r="G95" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F95" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>1569</v>
-      </c>
-      <c r="G96" t="s">
+        <v>1531</v>
+      </c>
+      <c r="F96" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>1530</v>
-      </c>
-      <c r="G97" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F97" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>868</v>
       </c>
-      <c r="G98" t="s">
+      <c r="F98" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>1531</v>
-      </c>
-      <c r="G99" t="s">
+        <v>1493</v>
+      </c>
+      <c r="F99" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>1570</v>
-      </c>
-      <c r="G100" t="s">
+        <v>1532</v>
+      </c>
+      <c r="F100" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>1532</v>
-      </c>
-      <c r="G101" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F101" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>1571</v>
-      </c>
-      <c r="G102" t="s">
+        <v>1533</v>
+      </c>
+      <c r="F102" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>1533</v>
-      </c>
-      <c r="G103" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F103" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>869</v>
       </c>
-      <c r="G104" t="s">
+      <c r="F104" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>870</v>
       </c>
-      <c r="G105" t="s">
+      <c r="F105" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>1572</v>
-      </c>
-      <c r="G106" t="s">
+        <v>1534</v>
+      </c>
+      <c r="F106" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>1534</v>
-      </c>
-      <c r="G107" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F107" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>1573</v>
-      </c>
-      <c r="G108" t="s">
+        <v>1535</v>
+      </c>
+      <c r="F108" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>1535</v>
-      </c>
-      <c r="G109" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F109" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>1574</v>
-      </c>
-      <c r="G110" t="s">
+        <v>1536</v>
+      </c>
+      <c r="F110" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>1536</v>
-      </c>
-      <c r="G111" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F111" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>871</v>
       </c>
-      <c r="G112" t="s">
+      <c r="F112" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>872</v>
       </c>
-      <c r="G113" t="s">
+      <c r="F113" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>1575</v>
-      </c>
-      <c r="G114" t="s">
+        <v>1537</v>
+      </c>
+      <c r="F114" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>1537</v>
-      </c>
-      <c r="G115" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F115" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>1576</v>
-      </c>
-      <c r="G116" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F116" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>1538</v>
-      </c>
-      <c r="G117" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F117" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>1577</v>
-      </c>
-      <c r="G118" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F118" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>1539</v>
-      </c>
-      <c r="G119" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F119" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>1578</v>
-      </c>
-      <c r="G120" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F120" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>1540</v>
-      </c>
-      <c r="G121" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F121" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>873</v>
       </c>
-      <c r="G122" t="s">
+      <c r="F122" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>874</v>
       </c>
-      <c r="G123" t="s">
+      <c r="F123" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>1579</v>
-      </c>
-      <c r="G124" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F124" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>1541</v>
-      </c>
-      <c r="G125" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F125" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>1580</v>
-      </c>
-      <c r="G126" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F126" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1542</v>
-      </c>
-      <c r="G127" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F127" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>875</v>
       </c>
-      <c r="G128" t="s">
+      <c r="F128" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>876</v>
       </c>
-      <c r="G129" t="s">
+      <c r="F129" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>1581</v>
-      </c>
-      <c r="G130" t="s">
+        <v>1543</v>
+      </c>
+      <c r="F130" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>1543</v>
-      </c>
-      <c r="G131" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F131" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>1582</v>
-      </c>
-      <c r="G132" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F132" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>1544</v>
-      </c>
-      <c r="G133" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F133" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>1583</v>
-      </c>
-      <c r="G134" t="s">
+        <v>1545</v>
+      </c>
+      <c r="F134" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>1545</v>
-      </c>
-      <c r="G135" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F135" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>1584</v>
-      </c>
-      <c r="G136" t="s">
+        <v>1546</v>
+      </c>
+      <c r="F136" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>1546</v>
-      </c>
-      <c r="G137" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F137" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>1585</v>
-      </c>
-      <c r="G138" t="s">
+        <v>1547</v>
+      </c>
+      <c r="F138" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>1547</v>
-      </c>
-      <c r="G139" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F139" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>1586</v>
-      </c>
-      <c r="G140" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F140" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>1548</v>
-      </c>
-      <c r="G141" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F141" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>1587</v>
-      </c>
-      <c r="G142" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F142" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>1549</v>
-      </c>
-      <c r="G143" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F143" t="s">
         <v>825</v>
       </c>
-      <c r="I143" s="2"/>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H143" s="2"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>1588</v>
-      </c>
-      <c r="G144" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F144" t="s">
         <v>826</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>1550</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>1589</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>1551</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>1590</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>1552</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>1591</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>1553</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>1592</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1554</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>1593</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1555</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>1594</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1556</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1595</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1557</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1596</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1558</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>1597</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1559</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>1598</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>1560</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>1599</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1561</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>1600</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>1562</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>1601</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>1563</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="172" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A172" s="5" t="s">
-        <v>1011</v>
+        <v>979</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>1012</v>
+        <v>980</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>1013</v>
+        <v>981</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>1014</v>
+        <v>982</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>1015</v>
+        <v>983</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>1016</v>
+        <v>984</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>1017</v>
+        <v>985</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1018</v>
+        <v>986</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>1019</v>
+        <v>987</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>1020</v>
+        <v>988</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>1021</v>
+        <v>989</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>1022</v>
+        <v>990</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>1023</v>
+        <v>991</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>1024</v>
+        <v>992</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>1025</v>
+        <v>993</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>1026</v>
+        <v>994</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>1027</v>
+        <v>995</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>1028</v>
+        <v>996</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>1029</v>
+        <v>997</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>1030</v>
+        <v>998</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>1031</v>
+        <v>999</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>1032</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>1033</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>1034</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>1035</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>1036</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>1037</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>1145</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>1602</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>1146</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>1147</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>1603</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>1148</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>1149</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>1150</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>1151</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>1152</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>1604</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>1153</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>1154</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>1155</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>1156</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>1157</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>1605</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>1158</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>1564</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>1159</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>1160</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1606</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>1161</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>1162</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>1163</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1164</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>1165</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1166</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1167</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1168</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>1607</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>1169</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>1170</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1608</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1171</v>
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>1717</v>
       </c>
     </row>
   </sheetData>
@@ -13696,7 +16660,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13BB4D98-1E3A-4E3C-ACBA-9B32A23C1612}">
-  <dimension ref="A1:A131"/>
+  <dimension ref="A1:A140"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -14063,298 +17027,343 @@
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
-        <v>982</v>
+      <c r="A73" t="s">
+        <v>950</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>983</v>
+        <v>951</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>984</v>
+        <v>952</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>985</v>
+        <v>953</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>986</v>
+        <v>954</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>987</v>
+        <v>955</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>988</v>
+        <v>956</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>989</v>
+        <v>957</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>990</v>
+        <v>958</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>991</v>
+        <v>959</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>992</v>
+        <v>960</v>
       </c>
     </row>
     <row r="84" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>993</v>
+        <v>961</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>994</v>
+        <v>962</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>995</v>
+        <v>963</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>996</v>
+        <v>964</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>997</v>
+        <v>965</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>998</v>
+        <v>966</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>999</v>
+        <v>967</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>1000</v>
+        <v>968</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>1001</v>
+        <v>969</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>1002</v>
+        <v>970</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>1003</v>
+        <v>971</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>1004</v>
+        <v>972</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>1005</v>
+        <v>973</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>1006</v>
+        <v>974</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>1007</v>
+        <v>975</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>1008</v>
+        <v>976</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>1009</v>
+        <v>977</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>1010</v>
+        <v>978</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>1616</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>1609</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>1172</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>1617</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>1610</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>1173</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>1174</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>1175</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>1176</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>1618</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>1611</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>1177</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>1619</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>1612</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>1178</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>1179</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>1180</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>1181</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>1620</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>1613</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>1182</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>1183</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>1184</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>1185</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>1621</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1614</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>1186</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>1622</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>1615</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>1187</v>
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>1713</v>
       </c>
     </row>
   </sheetData>
